--- a/docs/Attendance-Upload-Template.xlsx
+++ b/docs/Attendance-Upload-Template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\Personal\ChurchRegister\docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\ChurchRegister\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D3441D0-A7A3-4D47-9FA0-DAA8402DB5BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F9B3271-896E-4879-8EBC-DBC9CF1DCFEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19090" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{47F8AE6A-1A07-483D-912A-149763095AFE}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="11625" xr2:uid="{47F8AE6A-1A07-483D-912A-149763095AFE}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -31,12 +31,15 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
   <si>
     <t>Week Commecning (Sunday)</t>
   </si>
@@ -105,6 +108,9 @@
   </si>
   <si>
     <t>Saturday</t>
+  </si>
+  <si>
+    <t>Soup Station Bags</t>
   </si>
 </sst>
 </file>
@@ -191,12 +197,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -208,6 +208,12 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -543,841 +549,888 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20EEF58A-9C26-4AC5-86CB-1A994CC9BBB9}">
-  <dimension ref="A1:Q33"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:R33"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
-    <col min="2" max="3" width="16.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="16.53125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.21875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.19921875" bestFit="1" customWidth="1"/>
     <col min="6" max="7" width="16.33203125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="15.33203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.21875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.19921875" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="17.6640625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="12" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.109375" customWidth="1"/>
-    <col min="13" max="13" width="13.5546875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="10.88671875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="15.109375" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.1328125" customWidth="1"/>
+    <col min="14" max="14" width="13.53125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.86328125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="15.1328125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="10.53125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="18" x14ac:dyDescent="0.35">
-      <c r="A1" s="8" t="s">
+    <row r="1" spans="1:18" ht="18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2" t="s">
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
+      <c r="G1" s="7"/>
+      <c r="H1" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2" t="s">
+      <c r="I1" s="7"/>
+      <c r="J1" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2" t="s">
+      <c r="K1" s="7"/>
+      <c r="L1" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="M1" s="3"/>
-      <c r="N1" s="4" t="s">
+      <c r="M1" s="7"/>
+      <c r="N1" s="8"/>
+      <c r="O1" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="O1" s="4" t="s">
+      <c r="P1" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="P1" s="4" t="s">
+      <c r="Q1" s="2" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:17" ht="31.2" x14ac:dyDescent="0.35">
-      <c r="A2" s="8"/>
-      <c r="B2" s="5" t="s">
+    <row r="2" spans="1:18" ht="31.5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" s="6"/>
+      <c r="B2" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="G2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="H2" s="5" t="s">
+      <c r="H2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="I2" s="5" t="s">
+      <c r="I2" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="J2" s="5" t="s">
+      <c r="J2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K2" s="5" t="s">
+      <c r="K2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="L2" s="5" t="s">
+      <c r="L2" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="M2" s="5" t="s">
+      <c r="M2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="N2" s="5" t="s">
+      <c r="N2" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="O2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O2" s="5" t="s">
+      <c r="P2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="P2" s="5" t="s">
+      <c r="Q2" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="Q2" s="1"/>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A3" s="6">
+      <c r="R2" s="1"/>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="A3" s="4">
         <v>46026</v>
       </c>
-      <c r="B3" s="7">
+      <c r="B3" s="5">
         <v>223</v>
       </c>
-      <c r="C3" s="7">
+      <c r="C3" s="5">
         <v>100</v>
       </c>
-      <c r="D3" s="7">
+      <c r="D3" s="5">
         <v>15</v>
       </c>
-      <c r="E3" s="7">
+      <c r="E3" s="5">
         <v>20</v>
       </c>
-      <c r="F3" s="7">
+      <c r="F3" s="5">
         <v>45</v>
       </c>
-      <c r="G3" s="7">
+      <c r="G3" s="5">
         <v>8</v>
       </c>
-      <c r="H3" s="7">
+      <c r="H3" s="5">
         <v>200</v>
       </c>
-      <c r="I3" s="7"/>
-      <c r="J3" s="7">
+      <c r="I3" s="5"/>
+      <c r="J3" s="5">
         <v>55</v>
       </c>
-      <c r="K3" s="7">
+      <c r="K3" s="5">
         <v>18</v>
       </c>
-      <c r="L3" s="7">
+      <c r="L3" s="5">
         <v>10</v>
       </c>
-      <c r="M3" s="7">
+      <c r="M3" s="5">
         <v>27</v>
       </c>
-      <c r="N3" s="7">
+      <c r="N3" s="5">
+        <v>27</v>
+      </c>
+      <c r="O3" s="5">
         <v>15</v>
       </c>
-      <c r="O3" s="7">
+      <c r="P3" s="5">
         <v>6</v>
       </c>
-      <c r="P3" s="7"/>
-    </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A4" s="6">
+      <c r="Q3" s="5"/>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="A4" s="4">
         <v>46033</v>
       </c>
-      <c r="B4" s="7">
+      <c r="B4" s="5">
         <v>247</v>
       </c>
-      <c r="C4" s="7">
+      <c r="C4" s="5">
         <v>98</v>
       </c>
-      <c r="D4" s="7">
+      <c r="D4" s="5">
         <v>13</v>
       </c>
-      <c r="E4" s="7">
+      <c r="E4" s="5">
         <v>18</v>
       </c>
-      <c r="F4" s="7">
+      <c r="F4" s="5">
         <v>54</v>
       </c>
-      <c r="G4" s="7">
+      <c r="G4" s="5">
         <v>7</v>
       </c>
-      <c r="H4" s="7">
+      <c r="H4" s="5">
         <v>195</v>
       </c>
-      <c r="I4" s="7"/>
-      <c r="J4" s="7">
+      <c r="I4" s="5"/>
+      <c r="J4" s="5">
         <v>58</v>
       </c>
-      <c r="K4" s="7">
+      <c r="K4" s="5">
         <v>19</v>
       </c>
-      <c r="L4" s="7">
+      <c r="L4" s="5">
         <v>7</v>
       </c>
-      <c r="M4" s="7">
+      <c r="M4" s="5">
         <v>28</v>
       </c>
-      <c r="N4" s="7">
+      <c r="N4" s="5">
+        <v>28</v>
+      </c>
+      <c r="O4" s="5">
         <v>15</v>
       </c>
-      <c r="O4" s="7">
+      <c r="P4" s="5">
         <v>5</v>
       </c>
-      <c r="P4" s="7"/>
-    </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A5" s="6">
+      <c r="Q4" s="5"/>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="A5" s="4">
         <v>46040</v>
       </c>
-      <c r="B5" s="7">
+      <c r="B5" s="5">
         <v>201</v>
       </c>
-      <c r="C5" s="7">
+      <c r="C5" s="5">
         <v>110</v>
       </c>
-      <c r="D5" s="7">
+      <c r="D5" s="5">
         <v>6</v>
       </c>
-      <c r="E5" s="7">
+      <c r="E5" s="5">
         <v>17</v>
       </c>
-      <c r="F5" s="7">
+      <c r="F5" s="5">
         <v>58</v>
       </c>
-      <c r="G5" s="7">
+      <c r="G5" s="5">
         <v>8</v>
       </c>
-      <c r="H5" s="7">
+      <c r="H5" s="5">
         <v>180</v>
       </c>
-      <c r="I5" s="7">
+      <c r="I5" s="5">
         <v>14</v>
       </c>
-      <c r="J5" s="7">
+      <c r="J5" s="5">
         <v>63</v>
       </c>
-      <c r="K5" s="7">
+      <c r="K5" s="5">
         <v>21</v>
       </c>
-      <c r="L5" s="7">
+      <c r="L5" s="5">
         <v>8</v>
       </c>
-      <c r="M5" s="7">
+      <c r="M5" s="5">
         <v>24</v>
       </c>
-      <c r="N5" s="7">
+      <c r="N5" s="5">
+        <v>24</v>
+      </c>
+      <c r="O5" s="5">
         <v>14</v>
       </c>
-      <c r="O5" s="7">
+      <c r="P5" s="5">
         <v>5</v>
       </c>
-      <c r="P5" s="7"/>
-    </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A6" s="6">
+      <c r="Q5" s="5"/>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="A6" s="4">
         <v>46047</v>
       </c>
-      <c r="B6" s="7">
+      <c r="B6" s="5">
         <v>270</v>
       </c>
-      <c r="C6" s="7">
+      <c r="C6" s="5">
         <v>120</v>
       </c>
-      <c r="D6" s="7">
+      <c r="D6" s="5">
         <v>9</v>
       </c>
-      <c r="E6" s="7">
+      <c r="E6" s="5">
         <v>21</v>
       </c>
-      <c r="F6" s="7">
+      <c r="F6" s="5">
         <v>51</v>
       </c>
-      <c r="G6" s="7">
+      <c r="G6" s="5">
         <v>6</v>
       </c>
-      <c r="H6" s="7">
+      <c r="H6" s="5">
         <v>199</v>
       </c>
-      <c r="I6" s="7"/>
-      <c r="J6" s="7">
+      <c r="I6" s="5"/>
+      <c r="J6" s="5">
         <v>68</v>
       </c>
-      <c r="K6" s="7">
+      <c r="K6" s="5">
         <v>17</v>
       </c>
-      <c r="L6" s="7">
+      <c r="L6" s="5">
         <v>8</v>
       </c>
-      <c r="M6" s="7">
+      <c r="M6" s="5">
         <v>31</v>
       </c>
-      <c r="N6" s="7">
+      <c r="N6" s="5">
+        <v>31</v>
+      </c>
+      <c r="O6" s="5">
         <v>15</v>
       </c>
-      <c r="O6" s="7">
+      <c r="P6" s="5">
         <v>6</v>
       </c>
-      <c r="P6" s="7">
+      <c r="Q6" s="5">
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A7" s="6">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="A7" s="4">
         <v>46054</v>
       </c>
-      <c r="B7" s="7">
+      <c r="B7" s="5">
         <v>255</v>
       </c>
-      <c r="C7" s="7">
+      <c r="C7" s="5">
         <v>99</v>
       </c>
-      <c r="D7" s="7">
+      <c r="D7" s="5">
         <v>12</v>
       </c>
-      <c r="E7" s="7">
+      <c r="E7" s="5">
         <v>23</v>
       </c>
-      <c r="F7" s="7">
+      <c r="F7" s="5">
         <v>49</v>
       </c>
-      <c r="G7" s="7">
+      <c r="G7" s="5">
         <v>7</v>
       </c>
-      <c r="H7" s="7">
+      <c r="H7" s="5">
         <v>195</v>
       </c>
-      <c r="I7" s="7"/>
-      <c r="J7" s="7">
+      <c r="I7" s="5"/>
+      <c r="J7" s="5">
         <v>55</v>
       </c>
-      <c r="K7" s="7">
+      <c r="K7" s="5">
         <v>22</v>
       </c>
-      <c r="L7" s="7">
+      <c r="L7" s="5">
         <v>9</v>
       </c>
-      <c r="M7" s="7">
+      <c r="M7" s="5">
         <v>29</v>
       </c>
-      <c r="N7" s="7">
+      <c r="N7" s="5">
+        <v>29</v>
+      </c>
+      <c r="O7" s="5">
         <v>15</v>
       </c>
-      <c r="O7" s="7">
+      <c r="P7" s="5">
         <v>4</v>
       </c>
-      <c r="P7" s="7"/>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A8" s="6">
+      <c r="Q7" s="5"/>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="A8" s="4">
         <v>46061</v>
       </c>
-      <c r="B8" s="7">
+      <c r="B8" s="5">
         <v>268</v>
       </c>
-      <c r="C8" s="7">
+      <c r="C8" s="5">
         <v>103</v>
       </c>
-      <c r="D8" s="7">
+      <c r="D8" s="5">
         <v>16</v>
       </c>
-      <c r="E8" s="7">
+      <c r="E8" s="5">
         <v>21</v>
       </c>
-      <c r="F8" s="7">
+      <c r="F8" s="5">
         <v>56</v>
       </c>
-      <c r="G8" s="7">
+      <c r="G8" s="5">
         <v>8</v>
       </c>
-      <c r="H8" s="7">
+      <c r="H8" s="5">
         <v>203</v>
       </c>
-      <c r="I8" s="7"/>
-      <c r="J8" s="7">
+      <c r="I8" s="5"/>
+      <c r="J8" s="5">
         <v>58</v>
       </c>
-      <c r="K8" s="7">
+      <c r="K8" s="5">
         <v>17</v>
       </c>
-      <c r="L8" s="7">
+      <c r="L8" s="5">
         <v>10</v>
       </c>
-      <c r="M8" s="7">
+      <c r="M8" s="5">
         <v>30</v>
       </c>
-      <c r="N8" s="7">
+      <c r="N8" s="5">
+        <v>30</v>
+      </c>
+      <c r="O8" s="5">
         <v>14</v>
       </c>
-      <c r="O8" s="7">
+      <c r="P8" s="5">
         <v>7</v>
       </c>
-      <c r="P8" s="7"/>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A9" s="6">
+      <c r="Q8" s="5"/>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="A9" s="4">
         <v>46068</v>
       </c>
-      <c r="B9" s="7"/>
-      <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="7"/>
-      <c r="G9" s="7"/>
-      <c r="H9" s="7"/>
-      <c r="I9" s="7"/>
-      <c r="J9" s="7"/>
-      <c r="K9" s="7"/>
-      <c r="L9" s="7"/>
-      <c r="M9" s="7"/>
-      <c r="N9" s="7"/>
-      <c r="O9" s="7"/>
-      <c r="P9" s="7"/>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A10" s="6">
+      <c r="B9" s="5"/>
+      <c r="C9" s="5"/>
+      <c r="D9" s="5"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="5"/>
+      <c r="G9" s="5"/>
+      <c r="H9" s="5"/>
+      <c r="I9" s="5"/>
+      <c r="J9" s="5"/>
+      <c r="K9" s="5"/>
+      <c r="L9" s="5"/>
+      <c r="M9" s="5"/>
+      <c r="N9" s="5"/>
+      <c r="O9" s="5"/>
+      <c r="P9" s="5"/>
+      <c r="Q9" s="5"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="A10" s="4">
         <v>46075</v>
       </c>
-      <c r="B10" s="7"/>
-      <c r="C10" s="7"/>
-      <c r="D10" s="7"/>
-      <c r="E10" s="7"/>
-      <c r="F10" s="7"/>
-      <c r="G10" s="7"/>
-      <c r="H10" s="7"/>
-      <c r="I10" s="7"/>
-      <c r="J10" s="7"/>
-      <c r="K10" s="7"/>
-      <c r="L10" s="7"/>
-      <c r="M10" s="7"/>
-      <c r="N10" s="7"/>
-      <c r="O10" s="7"/>
-      <c r="P10" s="7"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A11" s="7"/>
-      <c r="B11" s="7"/>
-      <c r="C11" s="7"/>
-      <c r="D11" s="7"/>
-      <c r="E11" s="7"/>
-      <c r="F11" s="7"/>
-      <c r="G11" s="7"/>
-      <c r="H11" s="7"/>
-      <c r="I11" s="7"/>
-      <c r="J11" s="7"/>
-      <c r="K11" s="7"/>
-      <c r="L11" s="7"/>
-      <c r="M11" s="7"/>
-      <c r="N11" s="7"/>
-      <c r="O11" s="7"/>
-      <c r="P11" s="7"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A12" s="7"/>
-      <c r="B12" s="7"/>
-      <c r="C12" s="7"/>
-      <c r="D12" s="7"/>
-      <c r="E12" s="7"/>
-      <c r="F12" s="7"/>
-      <c r="G12" s="7"/>
-      <c r="H12" s="7"/>
-      <c r="I12" s="7"/>
-      <c r="J12" s="7"/>
-      <c r="K12" s="7"/>
-      <c r="L12" s="7"/>
-      <c r="M12" s="7"/>
-      <c r="N12" s="7"/>
-      <c r="O12" s="7"/>
-      <c r="P12" s="7"/>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A13" s="7"/>
-      <c r="B13" s="7"/>
-      <c r="C13" s="7"/>
-      <c r="D13" s="7"/>
-      <c r="E13" s="7"/>
-      <c r="F13" s="7"/>
-      <c r="G13" s="7"/>
-      <c r="H13" s="7"/>
-      <c r="I13" s="7"/>
-      <c r="J13" s="7"/>
-      <c r="K13" s="7"/>
-      <c r="L13" s="7"/>
-      <c r="M13" s="7"/>
-      <c r="N13" s="7"/>
-      <c r="O13" s="7"/>
-      <c r="P13" s="7"/>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A14" s="7"/>
-      <c r="B14" s="7"/>
-      <c r="C14" s="7"/>
-      <c r="D14" s="7"/>
-      <c r="E14" s="7"/>
-      <c r="F14" s="7"/>
-      <c r="G14" s="7"/>
-      <c r="H14" s="7"/>
-      <c r="I14" s="7"/>
-      <c r="J14" s="7"/>
-      <c r="K14" s="7"/>
-      <c r="L14" s="7"/>
-      <c r="M14" s="7"/>
-      <c r="N14" s="7"/>
-      <c r="O14" s="7"/>
-      <c r="P14" s="7"/>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A15" s="7"/>
-      <c r="B15" s="7"/>
-      <c r="C15" s="7"/>
-      <c r="D15" s="7"/>
-      <c r="E15" s="7"/>
-      <c r="F15" s="7"/>
-      <c r="G15" s="7"/>
-      <c r="H15" s="7"/>
-      <c r="I15" s="7"/>
-      <c r="J15" s="7"/>
-      <c r="K15" s="7"/>
-      <c r="L15" s="7"/>
-      <c r="M15" s="7"/>
-      <c r="N15" s="7"/>
-      <c r="O15" s="7"/>
-      <c r="P15" s="7"/>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A16" s="7"/>
-      <c r="B16" s="7"/>
-      <c r="C16" s="7"/>
-      <c r="D16" s="7"/>
-      <c r="E16" s="7"/>
-      <c r="F16" s="7"/>
-      <c r="G16" s="7"/>
-      <c r="H16" s="7"/>
-      <c r="I16" s="7"/>
-      <c r="J16" s="7"/>
-      <c r="K16" s="7"/>
-      <c r="L16" s="7"/>
-      <c r="M16" s="7"/>
-      <c r="N16" s="7"/>
-      <c r="O16" s="7"/>
-      <c r="P16" s="7"/>
-    </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A17" s="7"/>
-      <c r="B17" s="7"/>
-      <c r="C17" s="7"/>
-      <c r="D17" s="7"/>
-      <c r="E17" s="7"/>
-      <c r="F17" s="7"/>
-      <c r="G17" s="7"/>
-      <c r="H17" s="7"/>
-      <c r="I17" s="7"/>
-      <c r="J17" s="7"/>
-      <c r="K17" s="7"/>
-      <c r="L17" s="7"/>
-      <c r="M17" s="7"/>
-      <c r="N17" s="7"/>
-      <c r="O17" s="7"/>
-      <c r="P17" s="7"/>
-    </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A18" s="7"/>
-      <c r="B18" s="7"/>
-      <c r="C18" s="7"/>
-      <c r="D18" s="7"/>
-      <c r="E18" s="7"/>
-      <c r="F18" s="7"/>
-      <c r="G18" s="7"/>
-      <c r="H18" s="7"/>
-      <c r="I18" s="7"/>
-      <c r="J18" s="7"/>
-      <c r="K18" s="7"/>
-      <c r="L18" s="7"/>
-      <c r="M18" s="7"/>
-      <c r="N18" s="7"/>
-      <c r="O18" s="7"/>
-      <c r="P18" s="7"/>
-    </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A19" s="7"/>
-      <c r="B19" s="7"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="7"/>
-      <c r="F19" s="7"/>
-      <c r="G19" s="7"/>
-      <c r="H19" s="7"/>
-      <c r="I19" s="7"/>
-      <c r="J19" s="7"/>
-      <c r="K19" s="7"/>
-      <c r="L19" s="7"/>
-      <c r="M19" s="7"/>
-      <c r="N19" s="7"/>
-      <c r="O19" s="7"/>
-      <c r="P19" s="7"/>
-    </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A20" s="7"/>
-      <c r="B20" s="7"/>
-      <c r="C20" s="7"/>
-      <c r="D20" s="7"/>
-      <c r="E20" s="7"/>
-      <c r="F20" s="7"/>
-      <c r="G20" s="7"/>
-      <c r="H20" s="7"/>
-      <c r="I20" s="7"/>
-      <c r="J20" s="7"/>
-      <c r="K20" s="7"/>
-      <c r="L20" s="7"/>
-      <c r="M20" s="7"/>
-      <c r="N20" s="7"/>
-      <c r="O20" s="7"/>
-      <c r="P20" s="7"/>
-    </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A21" s="7"/>
-      <c r="B21" s="7"/>
-      <c r="C21" s="7"/>
-      <c r="D21" s="7"/>
-      <c r="E21" s="7"/>
-      <c r="F21" s="7"/>
-      <c r="G21" s="7"/>
-      <c r="H21" s="7"/>
-      <c r="I21" s="7"/>
-      <c r="J21" s="7"/>
-      <c r="K21" s="7"/>
-      <c r="L21" s="7"/>
-      <c r="M21" s="7"/>
-      <c r="N21" s="7"/>
-      <c r="O21" s="7"/>
-      <c r="P21" s="7"/>
-    </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A22" s="7"/>
-      <c r="B22" s="7"/>
-      <c r="C22" s="7"/>
-      <c r="D22" s="7"/>
-      <c r="E22" s="7"/>
-      <c r="F22" s="7"/>
-      <c r="G22" s="7"/>
-      <c r="H22" s="7"/>
-      <c r="I22" s="7"/>
-      <c r="J22" s="7"/>
-      <c r="K22" s="7"/>
-      <c r="L22" s="7"/>
-      <c r="M22" s="7"/>
-      <c r="N22" s="7"/>
-      <c r="O22" s="7"/>
-      <c r="P22" s="7"/>
-    </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A23" s="7"/>
-      <c r="B23" s="7"/>
-      <c r="C23" s="7"/>
-      <c r="D23" s="7"/>
-      <c r="E23" s="7"/>
-      <c r="F23" s="7"/>
-      <c r="G23" s="7"/>
-      <c r="H23" s="7"/>
-      <c r="I23" s="7"/>
-      <c r="J23" s="7"/>
-      <c r="K23" s="7"/>
-      <c r="L23" s="7"/>
-      <c r="M23" s="7"/>
-      <c r="N23" s="7"/>
-      <c r="O23" s="7"/>
-      <c r="P23" s="7"/>
-    </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A24" s="7"/>
-      <c r="B24" s="7"/>
-      <c r="C24" s="7"/>
-      <c r="D24" s="7"/>
-      <c r="E24" s="7"/>
-      <c r="F24" s="7"/>
-      <c r="G24" s="7"/>
-      <c r="H24" s="7"/>
-      <c r="I24" s="7"/>
-      <c r="J24" s="7"/>
-      <c r="K24" s="7"/>
-      <c r="L24" s="7"/>
-      <c r="M24" s="7"/>
-      <c r="N24" s="7"/>
-      <c r="O24" s="7"/>
-      <c r="P24" s="7"/>
-    </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A25" s="7"/>
-      <c r="B25" s="7"/>
-      <c r="C25" s="7"/>
-      <c r="D25" s="7"/>
-      <c r="E25" s="7"/>
-      <c r="F25" s="7"/>
-      <c r="G25" s="7"/>
-      <c r="H25" s="7"/>
-      <c r="I25" s="7"/>
-      <c r="J25" s="7"/>
-      <c r="K25" s="7"/>
-      <c r="L25" s="7"/>
-      <c r="M25" s="7"/>
-      <c r="N25" s="7"/>
-      <c r="O25" s="7"/>
-      <c r="P25" s="7"/>
-    </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A26" s="7"/>
-      <c r="B26" s="7"/>
-      <c r="C26" s="7"/>
-      <c r="D26" s="7"/>
-      <c r="E26" s="7"/>
-      <c r="F26" s="7"/>
-      <c r="G26" s="7"/>
-      <c r="H26" s="7"/>
-      <c r="I26" s="7"/>
-      <c r="J26" s="7"/>
-      <c r="K26" s="7"/>
-      <c r="L26" s="7"/>
-      <c r="M26" s="7"/>
-      <c r="N26" s="7"/>
-      <c r="O26" s="7"/>
-      <c r="P26" s="7"/>
-    </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A27" s="7"/>
-      <c r="B27" s="7"/>
-      <c r="C27" s="7"/>
-      <c r="D27" s="7"/>
-      <c r="E27" s="7"/>
-      <c r="F27" s="7"/>
-      <c r="G27" s="7"/>
-      <c r="H27" s="7"/>
-      <c r="I27" s="7"/>
-      <c r="J27" s="7"/>
-      <c r="K27" s="7"/>
-      <c r="L27" s="7"/>
-      <c r="M27" s="7"/>
-      <c r="N27" s="7"/>
-      <c r="O27" s="7"/>
-      <c r="P27" s="7"/>
-    </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A28" s="7"/>
-      <c r="B28" s="7"/>
-      <c r="C28" s="7"/>
-      <c r="D28" s="7"/>
-      <c r="E28" s="7"/>
-      <c r="F28" s="7"/>
-      <c r="G28" s="7"/>
-      <c r="H28" s="7"/>
-      <c r="I28" s="7"/>
-      <c r="J28" s="7"/>
-      <c r="K28" s="7"/>
-      <c r="L28" s="7"/>
-      <c r="M28" s="7"/>
-      <c r="N28" s="7"/>
-      <c r="O28" s="7"/>
-      <c r="P28" s="7"/>
-    </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A29" s="7"/>
-      <c r="B29" s="7"/>
-      <c r="C29" s="7"/>
-      <c r="D29" s="7"/>
-      <c r="E29" s="7"/>
-      <c r="F29" s="7"/>
-      <c r="G29" s="7"/>
-      <c r="H29" s="7"/>
-      <c r="I29" s="7"/>
-      <c r="J29" s="7"/>
-      <c r="K29" s="7"/>
-      <c r="L29" s="7"/>
-      <c r="M29" s="7"/>
-      <c r="N29" s="7"/>
-      <c r="O29" s="7"/>
-      <c r="P29" s="7"/>
-    </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A30" s="7"/>
-      <c r="B30" s="7"/>
-      <c r="C30" s="7"/>
-      <c r="D30" s="7"/>
-      <c r="E30" s="7"/>
-      <c r="F30" s="7"/>
-      <c r="G30" s="7"/>
-      <c r="H30" s="7"/>
-      <c r="I30" s="7"/>
-      <c r="J30" s="7"/>
-      <c r="K30" s="7"/>
-      <c r="L30" s="7"/>
-      <c r="M30" s="7"/>
-      <c r="N30" s="7"/>
-      <c r="O30" s="7"/>
-      <c r="P30" s="7"/>
-    </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A31" s="7"/>
-      <c r="B31" s="7"/>
-      <c r="C31" s="7"/>
-      <c r="D31" s="7"/>
-      <c r="E31" s="7"/>
-      <c r="F31" s="7"/>
-      <c r="G31" s="7"/>
-      <c r="H31" s="7"/>
-      <c r="I31" s="7"/>
-      <c r="J31" s="7"/>
-      <c r="K31" s="7"/>
-      <c r="L31" s="7"/>
-      <c r="M31" s="7"/>
-      <c r="N31" s="7"/>
-      <c r="O31" s="7"/>
-      <c r="P31" s="7"/>
-    </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A32" s="7"/>
-      <c r="B32" s="7"/>
-      <c r="C32" s="7"/>
-      <c r="D32" s="7"/>
-      <c r="E32" s="7"/>
-      <c r="F32" s="7"/>
-      <c r="G32" s="7"/>
-      <c r="H32" s="7"/>
-      <c r="I32" s="7"/>
-      <c r="J32" s="7"/>
-      <c r="K32" s="7"/>
-      <c r="L32" s="7"/>
-      <c r="M32" s="7"/>
-      <c r="N32" s="7"/>
-      <c r="O32" s="7"/>
-      <c r="P32" s="7"/>
-    </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A33" s="7"/>
-      <c r="B33" s="7"/>
-      <c r="C33" s="7"/>
-      <c r="D33" s="7"/>
-      <c r="E33" s="7"/>
-      <c r="F33" s="7"/>
-      <c r="G33" s="7"/>
-      <c r="H33" s="7"/>
-      <c r="I33" s="7"/>
-      <c r="J33" s="7"/>
-      <c r="K33" s="7"/>
-      <c r="L33" s="7"/>
-      <c r="M33" s="7"/>
-      <c r="N33" s="7"/>
-      <c r="O33" s="7"/>
-      <c r="P33" s="7"/>
+      <c r="B10" s="5"/>
+      <c r="C10" s="5"/>
+      <c r="D10" s="5"/>
+      <c r="E10" s="5"/>
+      <c r="F10" s="5"/>
+      <c r="G10" s="5"/>
+      <c r="H10" s="5"/>
+      <c r="I10" s="5"/>
+      <c r="J10" s="5"/>
+      <c r="K10" s="5"/>
+      <c r="L10" s="5"/>
+      <c r="M10" s="5"/>
+      <c r="N10" s="5"/>
+      <c r="O10" s="5"/>
+      <c r="P10" s="5"/>
+      <c r="Q10" s="5"/>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="A11" s="5"/>
+      <c r="B11" s="5"/>
+      <c r="C11" s="5"/>
+      <c r="D11" s="5"/>
+      <c r="E11" s="5"/>
+      <c r="F11" s="5"/>
+      <c r="G11" s="5"/>
+      <c r="H11" s="5"/>
+      <c r="I11" s="5"/>
+      <c r="J11" s="5"/>
+      <c r="K11" s="5"/>
+      <c r="L11" s="5"/>
+      <c r="M11" s="5"/>
+      <c r="N11" s="5"/>
+      <c r="O11" s="5"/>
+      <c r="P11" s="5"/>
+      <c r="Q11" s="5"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="A12" s="5"/>
+      <c r="B12" s="5"/>
+      <c r="C12" s="5"/>
+      <c r="D12" s="5"/>
+      <c r="E12" s="5"/>
+      <c r="F12" s="5"/>
+      <c r="G12" s="5"/>
+      <c r="H12" s="5"/>
+      <c r="I12" s="5"/>
+      <c r="J12" s="5"/>
+      <c r="K12" s="5"/>
+      <c r="L12" s="5"/>
+      <c r="M12" s="5"/>
+      <c r="N12" s="5"/>
+      <c r="O12" s="5"/>
+      <c r="P12" s="5"/>
+      <c r="Q12" s="5"/>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="A13" s="5"/>
+      <c r="B13" s="5"/>
+      <c r="C13" s="5"/>
+      <c r="D13" s="5"/>
+      <c r="E13" s="5"/>
+      <c r="F13" s="5"/>
+      <c r="G13" s="5"/>
+      <c r="H13" s="5"/>
+      <c r="I13" s="5"/>
+      <c r="J13" s="5"/>
+      <c r="K13" s="5"/>
+      <c r="L13" s="5"/>
+      <c r="M13" s="5"/>
+      <c r="N13" s="5"/>
+      <c r="O13" s="5"/>
+      <c r="P13" s="5"/>
+      <c r="Q13" s="5"/>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="A14" s="5"/>
+      <c r="B14" s="5"/>
+      <c r="C14" s="5"/>
+      <c r="D14" s="5"/>
+      <c r="E14" s="5"/>
+      <c r="F14" s="5"/>
+      <c r="G14" s="5"/>
+      <c r="H14" s="5"/>
+      <c r="I14" s="5"/>
+      <c r="J14" s="5"/>
+      <c r="K14" s="5"/>
+      <c r="L14" s="5"/>
+      <c r="M14" s="5"/>
+      <c r="N14" s="5"/>
+      <c r="O14" s="5"/>
+      <c r="P14" s="5"/>
+      <c r="Q14" s="5"/>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="A15" s="5"/>
+      <c r="B15" s="5"/>
+      <c r="C15" s="5"/>
+      <c r="D15" s="5"/>
+      <c r="E15" s="5"/>
+      <c r="F15" s="5"/>
+      <c r="G15" s="5"/>
+      <c r="H15" s="5"/>
+      <c r="I15" s="5"/>
+      <c r="J15" s="5"/>
+      <c r="K15" s="5"/>
+      <c r="L15" s="5"/>
+      <c r="M15" s="5"/>
+      <c r="N15" s="5"/>
+      <c r="O15" s="5"/>
+      <c r="P15" s="5"/>
+      <c r="Q15" s="5"/>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="A16" s="5"/>
+      <c r="B16" s="5"/>
+      <c r="C16" s="5"/>
+      <c r="D16" s="5"/>
+      <c r="E16" s="5"/>
+      <c r="F16" s="5"/>
+      <c r="G16" s="5"/>
+      <c r="H16" s="5"/>
+      <c r="I16" s="5"/>
+      <c r="J16" s="5"/>
+      <c r="K16" s="5"/>
+      <c r="L16" s="5"/>
+      <c r="M16" s="5"/>
+      <c r="N16" s="5"/>
+      <c r="O16" s="5"/>
+      <c r="P16" s="5"/>
+      <c r="Q16" s="5"/>
+    </row>
+    <row r="17" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="A17" s="5"/>
+      <c r="B17" s="5"/>
+      <c r="C17" s="5"/>
+      <c r="D17" s="5"/>
+      <c r="E17" s="5"/>
+      <c r="F17" s="5"/>
+      <c r="G17" s="5"/>
+      <c r="H17" s="5"/>
+      <c r="I17" s="5"/>
+      <c r="J17" s="5"/>
+      <c r="K17" s="5"/>
+      <c r="L17" s="5"/>
+      <c r="M17" s="5"/>
+      <c r="N17" s="5"/>
+      <c r="O17" s="5"/>
+      <c r="P17" s="5"/>
+      <c r="Q17" s="5"/>
+    </row>
+    <row r="18" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="A18" s="5"/>
+      <c r="B18" s="5"/>
+      <c r="C18" s="5"/>
+      <c r="D18" s="5"/>
+      <c r="E18" s="5"/>
+      <c r="F18" s="5"/>
+      <c r="G18" s="5"/>
+      <c r="H18" s="5"/>
+      <c r="I18" s="5"/>
+      <c r="J18" s="5"/>
+      <c r="K18" s="5"/>
+      <c r="L18" s="5"/>
+      <c r="M18" s="5"/>
+      <c r="N18" s="5"/>
+      <c r="O18" s="5"/>
+      <c r="P18" s="5"/>
+      <c r="Q18" s="5"/>
+    </row>
+    <row r="19" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="A19" s="5"/>
+      <c r="B19" s="5"/>
+      <c r="C19" s="5"/>
+      <c r="D19" s="5"/>
+      <c r="E19" s="5"/>
+      <c r="F19" s="5"/>
+      <c r="G19" s="5"/>
+      <c r="H19" s="5"/>
+      <c r="I19" s="5"/>
+      <c r="J19" s="5"/>
+      <c r="K19" s="5"/>
+      <c r="L19" s="5"/>
+      <c r="M19" s="5"/>
+      <c r="N19" s="5"/>
+      <c r="O19" s="5"/>
+      <c r="P19" s="5"/>
+      <c r="Q19" s="5"/>
+    </row>
+    <row r="20" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="A20" s="5"/>
+      <c r="B20" s="5"/>
+      <c r="C20" s="5"/>
+      <c r="D20" s="5"/>
+      <c r="E20" s="5"/>
+      <c r="F20" s="5"/>
+      <c r="G20" s="5"/>
+      <c r="H20" s="5"/>
+      <c r="I20" s="5"/>
+      <c r="J20" s="5"/>
+      <c r="K20" s="5"/>
+      <c r="L20" s="5"/>
+      <c r="M20" s="5"/>
+      <c r="N20" s="5"/>
+      <c r="O20" s="5"/>
+      <c r="P20" s="5"/>
+      <c r="Q20" s="5"/>
+    </row>
+    <row r="21" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="A21" s="5"/>
+      <c r="B21" s="5"/>
+      <c r="C21" s="5"/>
+      <c r="D21" s="5"/>
+      <c r="E21" s="5"/>
+      <c r="F21" s="5"/>
+      <c r="G21" s="5"/>
+      <c r="H21" s="5"/>
+      <c r="I21" s="5"/>
+      <c r="J21" s="5"/>
+      <c r="K21" s="5"/>
+      <c r="L21" s="5"/>
+      <c r="M21" s="5"/>
+      <c r="N21" s="5"/>
+      <c r="O21" s="5"/>
+      <c r="P21" s="5"/>
+      <c r="Q21" s="5"/>
+    </row>
+    <row r="22" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="A22" s="5"/>
+      <c r="B22" s="5"/>
+      <c r="C22" s="5"/>
+      <c r="D22" s="5"/>
+      <c r="E22" s="5"/>
+      <c r="F22" s="5"/>
+      <c r="G22" s="5"/>
+      <c r="H22" s="5"/>
+      <c r="I22" s="5"/>
+      <c r="J22" s="5"/>
+      <c r="K22" s="5"/>
+      <c r="L22" s="5"/>
+      <c r="M22" s="5"/>
+      <c r="N22" s="5"/>
+      <c r="O22" s="5"/>
+      <c r="P22" s="5"/>
+      <c r="Q22" s="5"/>
+    </row>
+    <row r="23" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="A23" s="5"/>
+      <c r="B23" s="5"/>
+      <c r="C23" s="5"/>
+      <c r="D23" s="5"/>
+      <c r="E23" s="5"/>
+      <c r="F23" s="5"/>
+      <c r="G23" s="5"/>
+      <c r="H23" s="5"/>
+      <c r="I23" s="5"/>
+      <c r="J23" s="5"/>
+      <c r="K23" s="5"/>
+      <c r="L23" s="5"/>
+      <c r="M23" s="5"/>
+      <c r="N23" s="5"/>
+      <c r="O23" s="5"/>
+      <c r="P23" s="5"/>
+      <c r="Q23" s="5"/>
+    </row>
+    <row r="24" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="A24" s="5"/>
+      <c r="B24" s="5"/>
+      <c r="C24" s="5"/>
+      <c r="D24" s="5"/>
+      <c r="E24" s="5"/>
+      <c r="F24" s="5"/>
+      <c r="G24" s="5"/>
+      <c r="H24" s="5"/>
+      <c r="I24" s="5"/>
+      <c r="J24" s="5"/>
+      <c r="K24" s="5"/>
+      <c r="L24" s="5"/>
+      <c r="M24" s="5"/>
+      <c r="N24" s="5"/>
+      <c r="O24" s="5"/>
+      <c r="P24" s="5"/>
+      <c r="Q24" s="5"/>
+    </row>
+    <row r="25" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="A25" s="5"/>
+      <c r="B25" s="5"/>
+      <c r="C25" s="5"/>
+      <c r="D25" s="5"/>
+      <c r="E25" s="5"/>
+      <c r="F25" s="5"/>
+      <c r="G25" s="5"/>
+      <c r="H25" s="5"/>
+      <c r="I25" s="5"/>
+      <c r="J25" s="5"/>
+      <c r="K25" s="5"/>
+      <c r="L25" s="5"/>
+      <c r="M25" s="5"/>
+      <c r="N25" s="5"/>
+      <c r="O25" s="5"/>
+      <c r="P25" s="5"/>
+      <c r="Q25" s="5"/>
+    </row>
+    <row r="26" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="A26" s="5"/>
+      <c r="B26" s="5"/>
+      <c r="C26" s="5"/>
+      <c r="D26" s="5"/>
+      <c r="E26" s="5"/>
+      <c r="F26" s="5"/>
+      <c r="G26" s="5"/>
+      <c r="H26" s="5"/>
+      <c r="I26" s="5"/>
+      <c r="J26" s="5"/>
+      <c r="K26" s="5"/>
+      <c r="L26" s="5"/>
+      <c r="M26" s="5"/>
+      <c r="N26" s="5"/>
+      <c r="O26" s="5"/>
+      <c r="P26" s="5"/>
+      <c r="Q26" s="5"/>
+    </row>
+    <row r="27" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="A27" s="5"/>
+      <c r="B27" s="5"/>
+      <c r="C27" s="5"/>
+      <c r="D27" s="5"/>
+      <c r="E27" s="5"/>
+      <c r="F27" s="5"/>
+      <c r="G27" s="5"/>
+      <c r="H27" s="5"/>
+      <c r="I27" s="5"/>
+      <c r="J27" s="5"/>
+      <c r="K27" s="5"/>
+      <c r="L27" s="5"/>
+      <c r="M27" s="5"/>
+      <c r="N27" s="5"/>
+      <c r="O27" s="5"/>
+      <c r="P27" s="5"/>
+      <c r="Q27" s="5"/>
+    </row>
+    <row r="28" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="A28" s="5"/>
+      <c r="B28" s="5"/>
+      <c r="C28" s="5"/>
+      <c r="D28" s="5"/>
+      <c r="E28" s="5"/>
+      <c r="F28" s="5"/>
+      <c r="G28" s="5"/>
+      <c r="H28" s="5"/>
+      <c r="I28" s="5"/>
+      <c r="J28" s="5"/>
+      <c r="K28" s="5"/>
+      <c r="L28" s="5"/>
+      <c r="M28" s="5"/>
+      <c r="N28" s="5"/>
+      <c r="O28" s="5"/>
+      <c r="P28" s="5"/>
+      <c r="Q28" s="5"/>
+    </row>
+    <row r="29" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="A29" s="5"/>
+      <c r="B29" s="5"/>
+      <c r="C29" s="5"/>
+      <c r="D29" s="5"/>
+      <c r="E29" s="5"/>
+      <c r="F29" s="5"/>
+      <c r="G29" s="5"/>
+      <c r="H29" s="5"/>
+      <c r="I29" s="5"/>
+      <c r="J29" s="5"/>
+      <c r="K29" s="5"/>
+      <c r="L29" s="5"/>
+      <c r="M29" s="5"/>
+      <c r="N29" s="5"/>
+      <c r="O29" s="5"/>
+      <c r="P29" s="5"/>
+      <c r="Q29" s="5"/>
+    </row>
+    <row r="30" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="A30" s="5"/>
+      <c r="B30" s="5"/>
+      <c r="C30" s="5"/>
+      <c r="D30" s="5"/>
+      <c r="E30" s="5"/>
+      <c r="F30" s="5"/>
+      <c r="G30" s="5"/>
+      <c r="H30" s="5"/>
+      <c r="I30" s="5"/>
+      <c r="J30" s="5"/>
+      <c r="K30" s="5"/>
+      <c r="L30" s="5"/>
+      <c r="M30" s="5"/>
+      <c r="N30" s="5"/>
+      <c r="O30" s="5"/>
+      <c r="P30" s="5"/>
+      <c r="Q30" s="5"/>
+    </row>
+    <row r="31" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="A31" s="5"/>
+      <c r="B31" s="5"/>
+      <c r="C31" s="5"/>
+      <c r="D31" s="5"/>
+      <c r="E31" s="5"/>
+      <c r="F31" s="5"/>
+      <c r="G31" s="5"/>
+      <c r="H31" s="5"/>
+      <c r="I31" s="5"/>
+      <c r="J31" s="5"/>
+      <c r="K31" s="5"/>
+      <c r="L31" s="5"/>
+      <c r="M31" s="5"/>
+      <c r="N31" s="5"/>
+      <c r="O31" s="5"/>
+      <c r="P31" s="5"/>
+      <c r="Q31" s="5"/>
+    </row>
+    <row r="32" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="A32" s="5"/>
+      <c r="B32" s="5"/>
+      <c r="C32" s="5"/>
+      <c r="D32" s="5"/>
+      <c r="E32" s="5"/>
+      <c r="F32" s="5"/>
+      <c r="G32" s="5"/>
+      <c r="H32" s="5"/>
+      <c r="I32" s="5"/>
+      <c r="J32" s="5"/>
+      <c r="K32" s="5"/>
+      <c r="L32" s="5"/>
+      <c r="M32" s="5"/>
+      <c r="N32" s="5"/>
+      <c r="O32" s="5"/>
+      <c r="P32" s="5"/>
+      <c r="Q32" s="5"/>
+    </row>
+    <row r="33" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="A33" s="5"/>
+      <c r="B33" s="5"/>
+      <c r="C33" s="5"/>
+      <c r="D33" s="5"/>
+      <c r="E33" s="5"/>
+      <c r="F33" s="5"/>
+      <c r="G33" s="5"/>
+      <c r="H33" s="5"/>
+      <c r="I33" s="5"/>
+      <c r="J33" s="5"/>
+      <c r="K33" s="5"/>
+      <c r="L33" s="5"/>
+      <c r="M33" s="5"/>
+      <c r="N33" s="5"/>
+      <c r="O33" s="5"/>
+      <c r="P33" s="5"/>
+      <c r="Q33" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -1385,7 +1438,7 @@
     <mergeCell ref="B1:G1"/>
     <mergeCell ref="J1:K1"/>
     <mergeCell ref="H1:I1"/>
-    <mergeCell ref="L1:M1"/>
+    <mergeCell ref="L1:N1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docs/Attendance-Upload-Template.xlsx
+++ b/docs/Attendance-Upload-Template.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\ChurchRegister\docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mtayl\iCloudDrive\Greenfield\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6A056FE-6DB9-490E-AD79-C3234917EA5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{513AAECA-1734-4292-960B-3CCC67A108BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="11625" xr2:uid="{47F8AE6A-1A07-483D-912A-149763095AFE}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
   <si>
     <t>Week Commecning (Sunday)</t>
   </si>
@@ -111,6 +111,9 @@
   </si>
   <si>
     <t>Soup Station Bags</t>
+  </si>
+  <si>
+    <t>Conference Call</t>
   </si>
 </sst>
 </file>
@@ -197,7 +200,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -212,6 +215,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -221,13 +233,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -564,7 +579,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20EEF58A-9C26-4AC5-86CB-1A994CC9BBB9}">
-  <dimension ref="A1:R33"/>
+  <dimension ref="A1:S33"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="11.1328125" customWidth="1"/>
@@ -572,57 +587,58 @@
     <col min="3" max="3" width="14.1328125" customWidth="1"/>
     <col min="4" max="4" width="8.59765625" customWidth="1"/>
     <col min="5" max="5" width="8.06640625" customWidth="1"/>
-    <col min="6" max="6" width="14.06640625" customWidth="1"/>
-    <col min="7" max="7" width="14.6640625" customWidth="1"/>
-    <col min="8" max="8" width="9.86328125" customWidth="1"/>
-    <col min="9" max="9" width="10.86328125" customWidth="1"/>
-    <col min="10" max="10" width="14.6640625" customWidth="1"/>
-    <col min="11" max="11" width="10.86328125" customWidth="1"/>
-    <col min="12" max="12" width="9.9296875" customWidth="1"/>
-    <col min="13" max="13" width="9.73046875" customWidth="1"/>
-    <col min="14" max="14" width="11.46484375" customWidth="1"/>
-    <col min="15" max="15" width="10.86328125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10.1328125" customWidth="1"/>
-    <col min="17" max="17" width="10.53125" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.06640625" customWidth="1"/>
+    <col min="8" max="8" width="9.9296875" customWidth="1"/>
+    <col min="9" max="9" width="9.86328125" customWidth="1"/>
+    <col min="10" max="10" width="10.86328125" customWidth="1"/>
+    <col min="11" max="11" width="14.6640625" customWidth="1"/>
+    <col min="12" max="12" width="10.86328125" customWidth="1"/>
+    <col min="13" max="13" width="9.9296875" customWidth="1"/>
+    <col min="14" max="14" width="9.73046875" customWidth="1"/>
+    <col min="15" max="15" width="11.46484375" customWidth="1"/>
+    <col min="16" max="16" width="10.86328125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="10.1328125" customWidth="1"/>
+    <col min="18" max="18" width="10.53125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="6" t="s">
+    <row r="1" spans="1:19" ht="18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7"/>
-      <c r="G1" s="7"/>
-      <c r="H1" s="7" t="s">
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="10"/>
+      <c r="I1" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="I1" s="7"/>
-      <c r="J1" s="7" t="s">
+      <c r="J1" s="10"/>
+      <c r="K1" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="K1" s="7"/>
-      <c r="L1" s="7" t="s">
+      <c r="L1" s="10"/>
+      <c r="M1" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="M1" s="7"/>
-      <c r="N1" s="8"/>
-      <c r="O1" s="2" t="s">
+      <c r="N1" s="10"/>
+      <c r="O1" s="11"/>
+      <c r="P1" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="Q1" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="R1" s="2" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:18" ht="31.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="6"/>
+    <row r="2" spans="1:19" ht="47.25" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" s="9"/>
       <c r="B2" s="3" t="s">
         <v>3</v>
       </c>
@@ -641,599 +657,683 @@
       <c r="G2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="H2" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="I2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="J2" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="J2" s="3" t="s">
+      <c r="K2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K2" s="3" t="s">
+      <c r="L2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="L2" s="3" t="s">
+      <c r="M2" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="M2" s="3" t="s">
+      <c r="N2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="N2" s="3" t="s">
+      <c r="O2" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="O2" s="3" t="s">
+      <c r="P2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P2" s="3" t="s">
+      <c r="Q2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="Q2" s="3" t="s">
+      <c r="R2" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="R2" s="1"/>
-    </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.45">
-      <c r="A3" s="9">
+      <c r="S2" s="1"/>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="A3" s="13">
         <v>46026</v>
       </c>
-      <c r="B3" s="10">
+      <c r="B3" s="14">
         <v>250</v>
       </c>
-      <c r="C3" s="10">
+      <c r="C3" s="14">
         <v>81</v>
       </c>
-      <c r="D3" s="10">
+      <c r="D3" s="14">
         <v>8</v>
       </c>
-      <c r="E3" s="10">
+      <c r="E3" s="14">
         <v>17</v>
       </c>
-      <c r="F3" s="10">
+      <c r="F3" s="14">
         <v>41</v>
       </c>
-      <c r="G3" s="11"/>
-      <c r="H3" s="11"/>
-      <c r="I3" s="10">
+      <c r="G3" s="15"/>
+      <c r="H3" s="15"/>
+      <c r="I3" s="15"/>
+      <c r="J3" s="14">
         <v>46</v>
       </c>
-      <c r="J3" s="10">
+      <c r="K3" s="14">
         <v>14</v>
       </c>
-      <c r="K3" s="10">
+      <c r="L3" s="14">
         <v>11</v>
       </c>
-      <c r="L3" s="10">
+      <c r="M3" s="14">
         <v>41</v>
       </c>
-      <c r="M3" s="10">
+      <c r="N3" s="14">
         <v>46</v>
       </c>
-      <c r="N3" s="11"/>
-      <c r="O3" s="10">
+      <c r="O3" s="15"/>
+      <c r="P3" s="14">
         <v>5</v>
       </c>
-      <c r="P3" s="10">
+      <c r="Q3" s="14">
         <v>18</v>
       </c>
-      <c r="Q3" s="5"/>
-    </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.45">
-      <c r="A4" s="9">
+      <c r="R3" s="5"/>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="A4" s="13">
         <v>46033</v>
       </c>
-      <c r="B4" s="10">
+      <c r="B4" s="14">
         <v>250</v>
       </c>
-      <c r="C4" s="10">
+      <c r="C4" s="14">
         <v>81</v>
       </c>
-      <c r="D4" s="10">
+      <c r="D4" s="14">
         <v>8</v>
       </c>
-      <c r="E4" s="10">
+      <c r="E4" s="14">
         <v>17</v>
       </c>
-      <c r="F4" s="10">
+      <c r="F4" s="14">
         <v>41</v>
       </c>
-      <c r="G4" s="11"/>
-      <c r="H4" s="11"/>
-      <c r="I4" s="10">
+      <c r="G4" s="15"/>
+      <c r="H4" s="15"/>
+      <c r="I4" s="15"/>
+      <c r="J4" s="14">
         <v>46</v>
       </c>
-      <c r="J4" s="10">
+      <c r="K4" s="14">
         <v>14</v>
       </c>
-      <c r="K4" s="10">
+      <c r="L4" s="14">
         <v>11</v>
       </c>
-      <c r="L4" s="10">
+      <c r="M4" s="14">
         <v>41</v>
       </c>
-      <c r="M4" s="10">
+      <c r="N4" s="14">
         <v>46</v>
       </c>
-      <c r="N4" s="10">
+      <c r="O4" s="14">
         <v>16</v>
       </c>
-      <c r="O4" s="10">
+      <c r="P4" s="14">
         <v>5</v>
       </c>
-      <c r="P4" s="11"/>
-      <c r="Q4" s="5"/>
-    </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.45">
-      <c r="A5" s="9">
+      <c r="Q4" s="15"/>
+      <c r="R4" s="5"/>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="A5" s="13">
         <v>46040</v>
       </c>
-      <c r="B5" s="10">
+      <c r="B5" s="14">
         <v>250</v>
       </c>
-      <c r="C5" s="10">
+      <c r="C5" s="14">
         <v>81</v>
       </c>
-      <c r="D5" s="10">
+      <c r="D5" s="14">
         <v>8</v>
       </c>
-      <c r="E5" s="10">
+      <c r="E5" s="14">
         <v>17</v>
       </c>
-      <c r="F5" s="10">
+      <c r="F5" s="14">
         <v>41</v>
       </c>
-      <c r="G5" s="11"/>
-      <c r="H5" s="10">
+      <c r="G5" s="15"/>
+      <c r="H5" s="15"/>
+      <c r="I5" s="14">
         <v>10</v>
       </c>
-      <c r="I5" s="10">
+      <c r="J5" s="14">
         <v>46</v>
       </c>
-      <c r="J5" s="10">
+      <c r="K5" s="14">
         <v>14</v>
       </c>
-      <c r="K5" s="10">
+      <c r="L5" s="14">
         <v>11</v>
       </c>
-      <c r="L5" s="10">
+      <c r="M5" s="14">
         <v>41</v>
       </c>
-      <c r="M5" s="10">
+      <c r="N5" s="14">
         <v>46</v>
       </c>
-      <c r="N5" s="10">
+      <c r="O5" s="14">
         <v>16</v>
       </c>
-      <c r="O5" s="10">
+      <c r="P5" s="14">
         <v>5</v>
       </c>
-      <c r="P5" s="11"/>
-      <c r="Q5" s="5"/>
-    </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.45">
-      <c r="A6" s="9">
+      <c r="Q5" s="15"/>
+      <c r="R5" s="5"/>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="A6" s="13">
         <v>46047</v>
       </c>
-      <c r="B6" s="10">
+      <c r="B6" s="14">
         <v>250</v>
       </c>
-      <c r="C6" s="10">
+      <c r="C6" s="14">
         <v>81</v>
       </c>
-      <c r="D6" s="10">
+      <c r="D6" s="14">
         <v>8</v>
       </c>
-      <c r="E6" s="10">
+      <c r="E6" s="14">
         <v>17</v>
       </c>
-      <c r="F6" s="10">
+      <c r="F6" s="14">
         <v>41</v>
       </c>
-      <c r="G6" s="11"/>
-      <c r="H6" s="11"/>
-      <c r="I6" s="10">
+      <c r="G6" s="15"/>
+      <c r="H6" s="15"/>
+      <c r="I6" s="15"/>
+      <c r="J6" s="14">
         <v>46</v>
       </c>
-      <c r="J6" s="10">
+      <c r="K6" s="14">
         <v>14</v>
       </c>
-      <c r="K6" s="10">
+      <c r="L6" s="14">
         <v>11</v>
       </c>
-      <c r="L6" s="10">
+      <c r="M6" s="14">
         <v>41</v>
       </c>
-      <c r="M6" s="10">
+      <c r="N6" s="14">
         <v>46</v>
       </c>
-      <c r="N6" s="10">
+      <c r="O6" s="14">
         <v>16</v>
       </c>
-      <c r="O6" s="10">
+      <c r="P6" s="14">
         <v>5</v>
       </c>
-      <c r="P6" s="10">
+      <c r="Q6" s="14">
         <v>14</v>
       </c>
-      <c r="Q6" s="5">
+      <c r="R6" s="5">
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.45">
-      <c r="A7" s="9">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="A7" s="13">
         <v>46054</v>
       </c>
-      <c r="B7" s="10">
+      <c r="B7" s="14">
         <v>210</v>
       </c>
-      <c r="C7" s="10">
+      <c r="C7" s="14">
         <v>102</v>
       </c>
-      <c r="D7" s="10">
+      <c r="D7" s="14">
         <v>10</v>
       </c>
-      <c r="E7" s="10">
+      <c r="E7" s="14">
         <v>23</v>
       </c>
-      <c r="F7" s="10">
+      <c r="F7" s="14">
         <v>47</v>
       </c>
-      <c r="G7" s="11"/>
-      <c r="H7" s="11"/>
-      <c r="I7" s="10">
+      <c r="G7" s="15"/>
+      <c r="H7" s="15"/>
+      <c r="I7" s="15"/>
+      <c r="J7" s="14">
         <v>63</v>
       </c>
-      <c r="J7" s="10">
+      <c r="K7" s="14">
         <v>30</v>
       </c>
-      <c r="K7" s="10">
+      <c r="L7" s="14">
         <v>10</v>
       </c>
-      <c r="L7" s="10">
+      <c r="M7" s="14">
         <v>46</v>
       </c>
-      <c r="M7" s="10">
+      <c r="N7" s="14">
         <v>50</v>
       </c>
-      <c r="N7" s="11"/>
-      <c r="O7" s="10">
+      <c r="O7" s="15"/>
+      <c r="P7" s="14">
         <v>3</v>
       </c>
-      <c r="P7" s="11"/>
-      <c r="Q7" s="5"/>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.45">
-      <c r="A8" s="9">
+      <c r="Q7" s="15"/>
+      <c r="R7" s="5"/>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="A8" s="13">
         <v>46061</v>
       </c>
-      <c r="B8" s="10">
+      <c r="B8" s="14">
         <v>210</v>
       </c>
-      <c r="C8" s="10">
+      <c r="C8" s="14">
         <v>102</v>
       </c>
-      <c r="D8" s="10">
+      <c r="D8" s="14">
         <v>10</v>
       </c>
-      <c r="E8" s="10">
+      <c r="E8" s="14">
         <v>23</v>
       </c>
-      <c r="F8" s="10">
+      <c r="F8" s="14">
         <v>47</v>
       </c>
-      <c r="G8" s="11"/>
-      <c r="H8" s="11"/>
-      <c r="I8" s="10">
+      <c r="G8" s="15"/>
+      <c r="H8" s="15"/>
+      <c r="I8" s="15"/>
+      <c r="J8" s="14">
         <v>63</v>
       </c>
-      <c r="J8" s="10">
+      <c r="K8" s="14">
         <v>30</v>
       </c>
-      <c r="K8" s="10">
+      <c r="L8" s="14">
         <v>10</v>
       </c>
-      <c r="L8" s="10">
+      <c r="M8" s="14">
         <v>46</v>
       </c>
-      <c r="M8" s="10">
+      <c r="N8" s="14">
         <v>50</v>
       </c>
-      <c r="N8" s="10">
+      <c r="O8" s="14">
         <v>16</v>
       </c>
-      <c r="O8" s="10">
+      <c r="P8" s="14">
         <v>3</v>
       </c>
-      <c r="P8" s="11"/>
-      <c r="Q8" s="5"/>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.45">
-      <c r="A9" s="9">
+      <c r="Q8" s="15"/>
+      <c r="R8" s="5"/>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="A9" s="13">
         <v>46068</v>
       </c>
-      <c r="B9" s="10">
+      <c r="B9" s="14">
         <v>210</v>
       </c>
-      <c r="C9" s="10">
+      <c r="C9" s="14">
         <v>102</v>
       </c>
-      <c r="D9" s="10">
+      <c r="D9" s="14">
         <v>10</v>
       </c>
-      <c r="E9" s="10">
+      <c r="E9" s="14">
         <v>23</v>
       </c>
-      <c r="F9" s="10">
+      <c r="F9" s="14">
         <v>47</v>
       </c>
-      <c r="G9" s="11"/>
-      <c r="H9" s="10">
+      <c r="G9" s="15"/>
+      <c r="H9" s="15"/>
+      <c r="I9" s="14">
         <v>11</v>
       </c>
-      <c r="I9" s="10">
+      <c r="J9" s="14">
         <v>63</v>
       </c>
-      <c r="J9" s="10">
+      <c r="K9" s="14">
         <v>30</v>
       </c>
-      <c r="K9" s="10">
+      <c r="L9" s="14">
         <v>10</v>
       </c>
-      <c r="L9" s="10">
+      <c r="M9" s="14">
         <v>46</v>
       </c>
-      <c r="M9" s="10">
+      <c r="N9" s="14">
         <v>50</v>
       </c>
-      <c r="N9" s="10">
+      <c r="O9" s="14">
         <v>16</v>
       </c>
-      <c r="O9" s="10">
+      <c r="P9" s="14">
         <v>3</v>
       </c>
-      <c r="P9" s="11"/>
-      <c r="Q9" s="5"/>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.45">
-      <c r="A10" s="9">
+      <c r="Q9" s="15"/>
+      <c r="R9" s="5"/>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="A10" s="13">
         <v>46075</v>
       </c>
-      <c r="B10" s="10">
+      <c r="B10" s="14">
         <v>210</v>
       </c>
-      <c r="C10" s="10">
+      <c r="C10" s="14">
         <v>102</v>
       </c>
-      <c r="D10" s="10">
+      <c r="D10" s="14">
         <v>10</v>
       </c>
-      <c r="E10" s="10">
+      <c r="E10" s="14">
         <v>23</v>
       </c>
-      <c r="F10" s="10">
+      <c r="F10" s="14">
         <v>47</v>
       </c>
-      <c r="G10" s="11"/>
-      <c r="H10" s="11"/>
-      <c r="I10" s="10">
+      <c r="G10" s="15"/>
+      <c r="H10" s="15"/>
+      <c r="I10" s="15"/>
+      <c r="J10" s="14">
         <v>63</v>
       </c>
-      <c r="J10" s="10">
+      <c r="K10" s="14">
         <v>30</v>
       </c>
-      <c r="K10" s="10">
+      <c r="L10" s="14">
         <v>10</v>
       </c>
-      <c r="L10" s="10">
+      <c r="M10" s="14">
         <v>46</v>
       </c>
-      <c r="M10" s="10">
+      <c r="N10" s="14">
         <v>50</v>
       </c>
-      <c r="N10" s="10">
+      <c r="O10" s="14">
         <v>16</v>
       </c>
-      <c r="O10" s="11"/>
-      <c r="P10" s="11"/>
-      <c r="Q10" s="5"/>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.45">
-      <c r="A11" s="9">
+      <c r="P10" s="15"/>
+      <c r="Q10" s="15"/>
+      <c r="R10" s="5"/>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="A11" s="13">
         <v>46082</v>
       </c>
-      <c r="B11" s="11"/>
-      <c r="C11" s="11"/>
-      <c r="D11" s="11"/>
-      <c r="E11" s="11"/>
-      <c r="F11" s="11"/>
-      <c r="G11" s="11"/>
-      <c r="H11" s="11"/>
-      <c r="I11" s="11"/>
-      <c r="J11" s="11"/>
-      <c r="K11" s="11"/>
-      <c r="L11" s="11"/>
-      <c r="M11" s="11"/>
-      <c r="N11" s="11"/>
-      <c r="O11" s="11"/>
-      <c r="P11" s="11"/>
-      <c r="Q11" s="5"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.45">
-      <c r="A12" s="9">
+      <c r="B11" s="14">
+        <v>230</v>
+      </c>
+      <c r="C11" s="14">
+        <v>113</v>
+      </c>
+      <c r="D11" s="15"/>
+      <c r="E11" s="14">
+        <v>23</v>
+      </c>
+      <c r="F11" s="14">
+        <v>49</v>
+      </c>
+      <c r="G11" s="14">
+        <v>11</v>
+      </c>
+      <c r="H11" s="15"/>
+      <c r="I11" s="15"/>
+      <c r="J11" s="14">
+        <v>61</v>
+      </c>
+      <c r="K11" s="15"/>
+      <c r="L11" s="15"/>
+      <c r="M11" s="15"/>
+      <c r="N11" s="15"/>
+      <c r="O11" s="15"/>
+      <c r="P11" s="15"/>
+      <c r="Q11" s="15"/>
+      <c r="R11" s="5"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="A12" s="13">
         <v>46089</v>
       </c>
-      <c r="B12" s="11"/>
-      <c r="C12" s="11"/>
-      <c r="D12" s="11"/>
-      <c r="E12" s="11"/>
-      <c r="F12" s="11"/>
-      <c r="G12" s="11"/>
-      <c r="H12" s="11"/>
-      <c r="I12" s="11"/>
-      <c r="J12" s="11"/>
-      <c r="K12" s="11"/>
-      <c r="L12" s="11"/>
-      <c r="M12" s="11"/>
-      <c r="N12" s="11"/>
-      <c r="O12" s="11"/>
-      <c r="P12" s="11"/>
-      <c r="Q12" s="5"/>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.45">
-      <c r="A13" s="9">
+      <c r="B12" s="14">
+        <v>229</v>
+      </c>
+      <c r="C12" s="14">
+        <v>105</v>
+      </c>
+      <c r="D12" s="15"/>
+      <c r="E12" s="14">
+        <v>23</v>
+      </c>
+      <c r="F12" s="14">
+        <v>47</v>
+      </c>
+      <c r="G12" s="14">
+        <v>8</v>
+      </c>
+      <c r="H12" s="15"/>
+      <c r="I12" s="15"/>
+      <c r="J12" s="14">
+        <v>65</v>
+      </c>
+      <c r="K12" s="15"/>
+      <c r="L12" s="15"/>
+      <c r="M12" s="15"/>
+      <c r="N12" s="15"/>
+      <c r="O12" s="15"/>
+      <c r="P12" s="15"/>
+      <c r="Q12" s="15"/>
+      <c r="R12" s="5"/>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="A13" s="13">
         <v>46096</v>
       </c>
-      <c r="B13" s="11"/>
-      <c r="C13" s="11"/>
-      <c r="D13" s="11"/>
-      <c r="E13" s="11"/>
-      <c r="F13" s="11"/>
-      <c r="G13" s="11"/>
-      <c r="H13" s="11"/>
-      <c r="I13" s="11"/>
-      <c r="J13" s="11"/>
-      <c r="K13" s="11"/>
-      <c r="L13" s="11"/>
-      <c r="M13" s="11"/>
-      <c r="N13" s="11"/>
-      <c r="O13" s="11"/>
-      <c r="P13" s="11"/>
-      <c r="Q13" s="5"/>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.45">
-      <c r="A14" s="9">
+      <c r="B13" s="14">
+        <v>218</v>
+      </c>
+      <c r="C13" s="14">
+        <v>119</v>
+      </c>
+      <c r="D13" s="15"/>
+      <c r="E13" s="14">
+        <v>23</v>
+      </c>
+      <c r="F13" s="14">
+        <v>37</v>
+      </c>
+      <c r="G13" s="14">
+        <v>10</v>
+      </c>
+      <c r="H13" s="14">
+        <v>185</v>
+      </c>
+      <c r="I13" s="15"/>
+      <c r="J13" s="14">
+        <v>69</v>
+      </c>
+      <c r="K13" s="15"/>
+      <c r="L13" s="15"/>
+      <c r="M13" s="15"/>
+      <c r="N13" s="15"/>
+      <c r="O13" s="15"/>
+      <c r="P13" s="15"/>
+      <c r="Q13" s="15"/>
+      <c r="R13" s="5"/>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="A14" s="13">
         <v>46103</v>
       </c>
-      <c r="B14" s="11"/>
-      <c r="C14" s="11"/>
-      <c r="D14" s="11"/>
-      <c r="E14" s="11"/>
-      <c r="F14" s="11"/>
-      <c r="G14" s="11"/>
-      <c r="H14" s="11"/>
-      <c r="I14" s="11"/>
-      <c r="J14" s="11"/>
-      <c r="K14" s="11"/>
-      <c r="L14" s="11"/>
-      <c r="M14" s="11"/>
-      <c r="N14" s="11"/>
-      <c r="O14" s="11"/>
-      <c r="P14" s="11"/>
-      <c r="Q14" s="5"/>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.45">
-      <c r="A15" s="9">
+      <c r="B14" s="14">
+        <v>233</v>
+      </c>
+      <c r="C14" s="14">
+        <v>108</v>
+      </c>
+      <c r="D14" s="15"/>
+      <c r="E14" s="14">
+        <v>18</v>
+      </c>
+      <c r="F14" s="14">
+        <v>44</v>
+      </c>
+      <c r="G14" s="14">
+        <v>8</v>
+      </c>
+      <c r="H14" s="14">
+        <v>324</v>
+      </c>
+      <c r="I14" s="15"/>
+      <c r="J14" s="14">
+        <v>55</v>
+      </c>
+      <c r="K14" s="15"/>
+      <c r="L14" s="15"/>
+      <c r="M14" s="15"/>
+      <c r="N14" s="15"/>
+      <c r="O14" s="15"/>
+      <c r="P14" s="15"/>
+      <c r="Q14" s="15"/>
+      <c r="R14" s="5"/>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="A15" s="13">
         <v>46110</v>
       </c>
-      <c r="B15" s="11"/>
-      <c r="C15" s="11"/>
-      <c r="D15" s="11"/>
-      <c r="E15" s="11"/>
-      <c r="F15" s="11"/>
-      <c r="G15" s="11"/>
-      <c r="H15" s="11"/>
-      <c r="I15" s="11"/>
-      <c r="J15" s="11"/>
-      <c r="K15" s="11"/>
-      <c r="L15" s="11"/>
-      <c r="M15" s="11"/>
-      <c r="N15" s="11"/>
-      <c r="O15" s="11"/>
-      <c r="P15" s="11"/>
-      <c r="Q15" s="5"/>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.45">
-      <c r="A16" s="9">
+      <c r="B15" s="14">
+        <v>213</v>
+      </c>
+      <c r="C15" s="14">
+        <v>105</v>
+      </c>
+      <c r="D15" s="15"/>
+      <c r="E15" s="14">
+        <v>21</v>
+      </c>
+      <c r="F15" s="14">
+        <v>78</v>
+      </c>
+      <c r="G15" s="14">
+        <v>8</v>
+      </c>
+      <c r="H15" s="15"/>
+      <c r="I15" s="15"/>
+      <c r="J15" s="14">
+        <v>60</v>
+      </c>
+      <c r="K15" s="15"/>
+      <c r="L15" s="15"/>
+      <c r="M15" s="15"/>
+      <c r="N15" s="15"/>
+      <c r="O15" s="15"/>
+      <c r="P15" s="15"/>
+      <c r="Q15" s="15"/>
+      <c r="R15" s="5"/>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="A16" s="13">
         <v>46117</v>
       </c>
-      <c r="B16" s="11"/>
-      <c r="C16" s="11"/>
-      <c r="D16" s="11"/>
-      <c r="E16" s="11"/>
-      <c r="F16" s="11"/>
-      <c r="G16" s="11"/>
-      <c r="H16" s="11"/>
-      <c r="I16" s="11"/>
-      <c r="J16" s="11"/>
-      <c r="K16" s="11"/>
-      <c r="L16" s="11"/>
-      <c r="M16" s="11"/>
-      <c r="N16" s="11"/>
-      <c r="O16" s="11"/>
-      <c r="P16" s="11"/>
-      <c r="Q16" s="5"/>
-    </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="A17" s="9">
+      <c r="B16" s="15"/>
+      <c r="C16" s="15"/>
+      <c r="D16" s="15"/>
+      <c r="E16" s="15"/>
+      <c r="F16" s="15"/>
+      <c r="G16" s="15"/>
+      <c r="H16" s="15"/>
+      <c r="I16" s="15"/>
+      <c r="J16" s="15"/>
+      <c r="K16" s="15"/>
+      <c r="L16" s="15"/>
+      <c r="M16" s="15"/>
+      <c r="N16" s="15"/>
+      <c r="O16" s="15"/>
+      <c r="P16" s="15"/>
+      <c r="Q16" s="15"/>
+      <c r="R16" s="5"/>
+    </row>
+    <row r="17" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="A17" s="7">
         <v>46124</v>
       </c>
-      <c r="B17" s="11"/>
-      <c r="C17" s="11"/>
-      <c r="D17" s="11"/>
-      <c r="E17" s="11"/>
-      <c r="F17" s="11"/>
-      <c r="G17" s="11"/>
-      <c r="H17" s="11"/>
-      <c r="I17" s="11"/>
-      <c r="J17" s="11"/>
-      <c r="K17" s="11"/>
-      <c r="L17" s="11"/>
-      <c r="M17" s="11"/>
-      <c r="N17" s="11"/>
-      <c r="O17" s="11"/>
-      <c r="P17" s="11"/>
-      <c r="Q17" s="5"/>
-    </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="A18" s="9">
+      <c r="B17" s="8"/>
+      <c r="C17" s="8"/>
+      <c r="D17" s="8"/>
+      <c r="E17" s="8"/>
+      <c r="F17" s="8"/>
+      <c r="G17" s="8"/>
+      <c r="H17" s="8"/>
+      <c r="I17" s="8"/>
+      <c r="J17" s="8"/>
+      <c r="K17" s="8"/>
+      <c r="L17" s="8"/>
+      <c r="M17" s="8"/>
+      <c r="N17" s="8"/>
+      <c r="O17" s="8"/>
+      <c r="P17" s="8"/>
+      <c r="Q17" s="8"/>
+      <c r="R17" s="5"/>
+    </row>
+    <row r="18" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="A18" s="7">
         <v>46131</v>
       </c>
-      <c r="B18" s="11"/>
-      <c r="C18" s="11"/>
-      <c r="D18" s="11"/>
-      <c r="E18" s="11"/>
-      <c r="F18" s="11"/>
-      <c r="G18" s="11"/>
-      <c r="H18" s="11"/>
-      <c r="I18" s="11"/>
-      <c r="J18" s="11"/>
-      <c r="K18" s="11"/>
-      <c r="L18" s="11"/>
-      <c r="M18" s="11"/>
-      <c r="N18" s="11"/>
-      <c r="O18" s="11"/>
-      <c r="P18" s="11"/>
-      <c r="Q18" s="5"/>
-    </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="A19" s="9">
+      <c r="B18" s="8"/>
+      <c r="C18" s="8"/>
+      <c r="D18" s="8"/>
+      <c r="E18" s="8"/>
+      <c r="F18" s="8"/>
+      <c r="G18" s="8"/>
+      <c r="H18" s="8"/>
+      <c r="I18" s="8"/>
+      <c r="J18" s="8"/>
+      <c r="K18" s="8"/>
+      <c r="L18" s="8"/>
+      <c r="M18" s="8"/>
+      <c r="N18" s="8"/>
+      <c r="O18" s="8"/>
+      <c r="P18" s="8"/>
+      <c r="Q18" s="8"/>
+      <c r="R18" s="5"/>
+    </row>
+    <row r="19" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="A19" s="7">
         <v>46079</v>
       </c>
-      <c r="B19" s="11"/>
-      <c r="C19" s="11"/>
-      <c r="D19" s="11"/>
-      <c r="E19" s="11"/>
-      <c r="F19" s="11"/>
-      <c r="G19" s="11"/>
-      <c r="H19" s="11"/>
-      <c r="I19" s="11"/>
-      <c r="J19" s="11"/>
-      <c r="K19" s="11"/>
-      <c r="L19" s="11"/>
-      <c r="M19" s="11"/>
-      <c r="N19" s="11"/>
-      <c r="O19" s="11"/>
-      <c r="P19" s="11"/>
-      <c r="Q19" s="5"/>
-    </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="B19" s="8"/>
+      <c r="C19" s="8"/>
+      <c r="D19" s="8"/>
+      <c r="E19" s="8"/>
+      <c r="F19" s="8"/>
+      <c r="G19" s="8"/>
+      <c r="H19" s="8"/>
+      <c r="I19" s="8"/>
+      <c r="J19" s="8"/>
+      <c r="K19" s="8"/>
+      <c r="L19" s="8"/>
+      <c r="M19" s="8"/>
+      <c r="N19" s="8"/>
+      <c r="O19" s="8"/>
+      <c r="P19" s="8"/>
+      <c r="Q19" s="8"/>
+      <c r="R19" s="5"/>
+    </row>
+    <row r="20" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A20" s="4"/>
       <c r="B20" s="4"/>
       <c r="C20" s="4"/>
       <c r="D20" s="4"/>
       <c r="E20" s="4"/>
       <c r="F20" s="4"/>
-      <c r="G20" s="4"/>
+      <c r="G20" s="6"/>
       <c r="H20" s="4"/>
       <c r="I20" s="4"/>
       <c r="J20" s="4"/>
@@ -1244,15 +1344,16 @@
       <c r="O20" s="4"/>
       <c r="P20" s="4"/>
       <c r="Q20" s="4"/>
-    </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="R20" s="4"/>
+    </row>
+    <row r="21" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A21" s="4"/>
       <c r="B21" s="4"/>
       <c r="C21" s="4"/>
       <c r="D21" s="4"/>
       <c r="E21" s="4"/>
       <c r="F21" s="4"/>
-      <c r="G21" s="4"/>
+      <c r="G21" s="6"/>
       <c r="H21" s="4"/>
       <c r="I21" s="4"/>
       <c r="J21" s="4"/>
@@ -1263,15 +1364,16 @@
       <c r="O21" s="4"/>
       <c r="P21" s="4"/>
       <c r="Q21" s="4"/>
-    </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="R21" s="4"/>
+    </row>
+    <row r="22" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A22" s="4"/>
       <c r="B22" s="4"/>
       <c r="C22" s="4"/>
       <c r="D22" s="4"/>
       <c r="E22" s="4"/>
       <c r="F22" s="4"/>
-      <c r="G22" s="4"/>
+      <c r="G22" s="6"/>
       <c r="H22" s="4"/>
       <c r="I22" s="4"/>
       <c r="J22" s="4"/>
@@ -1282,15 +1384,16 @@
       <c r="O22" s="4"/>
       <c r="P22" s="4"/>
       <c r="Q22" s="4"/>
-    </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="R22" s="4"/>
+    </row>
+    <row r="23" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A23" s="4"/>
       <c r="B23" s="4"/>
       <c r="C23" s="4"/>
       <c r="D23" s="4"/>
       <c r="E23" s="4"/>
       <c r="F23" s="4"/>
-      <c r="G23" s="4"/>
+      <c r="G23" s="6"/>
       <c r="H23" s="4"/>
       <c r="I23" s="4"/>
       <c r="J23" s="4"/>
@@ -1301,15 +1404,16 @@
       <c r="O23" s="4"/>
       <c r="P23" s="4"/>
       <c r="Q23" s="4"/>
-    </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="R23" s="4"/>
+    </row>
+    <row r="24" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A24" s="4"/>
       <c r="B24" s="4"/>
       <c r="C24" s="4"/>
       <c r="D24" s="4"/>
       <c r="E24" s="4"/>
       <c r="F24" s="4"/>
-      <c r="G24" s="4"/>
+      <c r="G24" s="6"/>
       <c r="H24" s="4"/>
       <c r="I24" s="4"/>
       <c r="J24" s="4"/>
@@ -1320,15 +1424,16 @@
       <c r="O24" s="4"/>
       <c r="P24" s="4"/>
       <c r="Q24" s="4"/>
-    </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="R24" s="4"/>
+    </row>
+    <row r="25" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A25" s="4"/>
       <c r="B25" s="4"/>
       <c r="C25" s="4"/>
       <c r="D25" s="4"/>
       <c r="E25" s="4"/>
       <c r="F25" s="4"/>
-      <c r="G25" s="4"/>
+      <c r="G25" s="6"/>
       <c r="H25" s="4"/>
       <c r="I25" s="4"/>
       <c r="J25" s="4"/>
@@ -1339,15 +1444,16 @@
       <c r="O25" s="4"/>
       <c r="P25" s="4"/>
       <c r="Q25" s="4"/>
-    </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="R25" s="4"/>
+    </row>
+    <row r="26" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A26" s="4"/>
       <c r="B26" s="4"/>
       <c r="C26" s="4"/>
       <c r="D26" s="4"/>
       <c r="E26" s="4"/>
       <c r="F26" s="4"/>
-      <c r="G26" s="4"/>
+      <c r="G26" s="6"/>
       <c r="H26" s="4"/>
       <c r="I26" s="4"/>
       <c r="J26" s="4"/>
@@ -1358,15 +1464,16 @@
       <c r="O26" s="4"/>
       <c r="P26" s="4"/>
       <c r="Q26" s="4"/>
-    </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="R26" s="4"/>
+    </row>
+    <row r="27" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A27" s="4"/>
       <c r="B27" s="4"/>
       <c r="C27" s="4"/>
       <c r="D27" s="4"/>
       <c r="E27" s="4"/>
       <c r="F27" s="4"/>
-      <c r="G27" s="4"/>
+      <c r="G27" s="6"/>
       <c r="H27" s="4"/>
       <c r="I27" s="4"/>
       <c r="J27" s="4"/>
@@ -1377,15 +1484,16 @@
       <c r="O27" s="4"/>
       <c r="P27" s="4"/>
       <c r="Q27" s="4"/>
-    </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="R27" s="4"/>
+    </row>
+    <row r="28" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A28" s="4"/>
       <c r="B28" s="4"/>
       <c r="C28" s="4"/>
       <c r="D28" s="4"/>
       <c r="E28" s="4"/>
       <c r="F28" s="4"/>
-      <c r="G28" s="4"/>
+      <c r="G28" s="6"/>
       <c r="H28" s="4"/>
       <c r="I28" s="4"/>
       <c r="J28" s="4"/>
@@ -1396,15 +1504,16 @@
       <c r="O28" s="4"/>
       <c r="P28" s="4"/>
       <c r="Q28" s="4"/>
-    </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="R28" s="4"/>
+    </row>
+    <row r="29" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A29" s="4"/>
       <c r="B29" s="4"/>
       <c r="C29" s="4"/>
       <c r="D29" s="4"/>
       <c r="E29" s="4"/>
       <c r="F29" s="4"/>
-      <c r="G29" s="4"/>
+      <c r="G29" s="6"/>
       <c r="H29" s="4"/>
       <c r="I29" s="4"/>
       <c r="J29" s="4"/>
@@ -1415,15 +1524,16 @@
       <c r="O29" s="4"/>
       <c r="P29" s="4"/>
       <c r="Q29" s="4"/>
-    </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="R29" s="4"/>
+    </row>
+    <row r="30" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A30" s="4"/>
       <c r="B30" s="4"/>
       <c r="C30" s="4"/>
       <c r="D30" s="4"/>
       <c r="E30" s="4"/>
       <c r="F30" s="4"/>
-      <c r="G30" s="4"/>
+      <c r="G30" s="6"/>
       <c r="H30" s="4"/>
       <c r="I30" s="4"/>
       <c r="J30" s="4"/>
@@ -1434,15 +1544,16 @@
       <c r="O30" s="4"/>
       <c r="P30" s="4"/>
       <c r="Q30" s="4"/>
-    </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="R30" s="4"/>
+    </row>
+    <row r="31" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A31" s="4"/>
       <c r="B31" s="4"/>
       <c r="C31" s="4"/>
       <c r="D31" s="4"/>
       <c r="E31" s="4"/>
       <c r="F31" s="4"/>
-      <c r="G31" s="4"/>
+      <c r="G31" s="6"/>
       <c r="H31" s="4"/>
       <c r="I31" s="4"/>
       <c r="J31" s="4"/>
@@ -1453,15 +1564,16 @@
       <c r="O31" s="4"/>
       <c r="P31" s="4"/>
       <c r="Q31" s="4"/>
-    </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="R31" s="4"/>
+    </row>
+    <row r="32" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A32" s="4"/>
       <c r="B32" s="4"/>
       <c r="C32" s="4"/>
       <c r="D32" s="4"/>
       <c r="E32" s="4"/>
       <c r="F32" s="4"/>
-      <c r="G32" s="4"/>
+      <c r="G32" s="6"/>
       <c r="H32" s="4"/>
       <c r="I32" s="4"/>
       <c r="J32" s="4"/>
@@ -1472,15 +1584,16 @@
       <c r="O32" s="4"/>
       <c r="P32" s="4"/>
       <c r="Q32" s="4"/>
-    </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="R32" s="4"/>
+    </row>
+    <row r="33" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A33" s="4"/>
       <c r="B33" s="4"/>
       <c r="C33" s="4"/>
       <c r="D33" s="4"/>
       <c r="E33" s="4"/>
       <c r="F33" s="4"/>
-      <c r="G33" s="4"/>
+      <c r="G33" s="6"/>
       <c r="H33" s="4"/>
       <c r="I33" s="4"/>
       <c r="J33" s="4"/>
@@ -1491,14 +1604,15 @@
       <c r="O33" s="4"/>
       <c r="P33" s="4"/>
       <c r="Q33" s="4"/>
+      <c r="R33" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:G1"/>
-    <mergeCell ref="J1:K1"/>
-    <mergeCell ref="H1:I1"/>
-    <mergeCell ref="L1:N1"/>
+    <mergeCell ref="B1:H1"/>
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="I1:J1"/>
+    <mergeCell ref="M1:O1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docs/Attendance-Upload-Template.xlsx
+++ b/docs/Attendance-Upload-Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mtayl\iCloudDrive\Greenfield\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{513AAECA-1734-4292-960B-3CCC67A108BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D9A0DDC-2E10-438A-898C-1CB527E72A6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="11625" xr2:uid="{47F8AE6A-1A07-483D-912A-149763095AFE}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
   <si>
     <t>Week Commecning (Sunday)</t>
   </si>
@@ -111,9 +111,6 @@
   </si>
   <si>
     <t>Soup Station Bags</t>
-  </si>
-  <si>
-    <t>Conference Call</t>
   </si>
 </sst>
 </file>
@@ -200,7 +197,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -224,6 +221,15 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -232,18 +238,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -579,7 +573,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20EEF58A-9C26-4AC5-86CB-1A994CC9BBB9}">
-  <dimension ref="A1:S33"/>
+  <dimension ref="A1:R33"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="11.1328125" customWidth="1"/>
@@ -588,57 +582,55 @@
     <col min="4" max="4" width="8.59765625" customWidth="1"/>
     <col min="5" max="5" width="8.06640625" customWidth="1"/>
     <col min="6" max="7" width="14.06640625" customWidth="1"/>
-    <col min="8" max="8" width="9.9296875" customWidth="1"/>
-    <col min="9" max="9" width="9.86328125" customWidth="1"/>
-    <col min="10" max="10" width="10.86328125" customWidth="1"/>
-    <col min="11" max="11" width="14.6640625" customWidth="1"/>
-    <col min="12" max="12" width="10.86328125" customWidth="1"/>
-    <col min="13" max="13" width="9.9296875" customWidth="1"/>
-    <col min="14" max="14" width="9.73046875" customWidth="1"/>
-    <col min="15" max="15" width="11.46484375" customWidth="1"/>
-    <col min="16" max="16" width="10.86328125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="10.1328125" customWidth="1"/>
-    <col min="18" max="18" width="10.53125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.86328125" customWidth="1"/>
+    <col min="9" max="9" width="10.86328125" customWidth="1"/>
+    <col min="10" max="10" width="14.6640625" customWidth="1"/>
+    <col min="11" max="11" width="10.86328125" customWidth="1"/>
+    <col min="12" max="12" width="9.9296875" customWidth="1"/>
+    <col min="13" max="13" width="9.73046875" customWidth="1"/>
+    <col min="14" max="14" width="11.46484375" customWidth="1"/>
+    <col min="15" max="15" width="10.86328125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.1328125" customWidth="1"/>
+    <col min="17" max="17" width="10.53125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="9" t="s">
+    <row r="1" spans="1:18" ht="18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
-      <c r="G1" s="10"/>
-      <c r="H1" s="10"/>
-      <c r="I1" s="10" t="s">
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="J1" s="10"/>
-      <c r="K1" s="10" t="s">
+      <c r="I1" s="13"/>
+      <c r="J1" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="L1" s="10"/>
-      <c r="M1" s="10" t="s">
+      <c r="K1" s="13"/>
+      <c r="L1" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="N1" s="10"/>
-      <c r="O1" s="11"/>
+      <c r="M1" s="13"/>
+      <c r="N1" s="14"/>
+      <c r="O1" s="2" t="s">
+        <v>19</v>
+      </c>
       <c r="P1" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Q1" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="R1" s="2" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:19" ht="47.25" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="9"/>
+    <row r="2" spans="1:18" ht="47.25" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" s="12"/>
       <c r="B2" s="3" t="s">
         <v>3</v>
       </c>
@@ -657,610 +649,591 @@
       <c r="G2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="H2" s="12" t="s">
-        <v>24</v>
+      <c r="H2" s="3" t="s">
+        <v>12</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="L2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="M2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="N2" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="O2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P2" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q2" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="R2" s="1"/>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="A3" s="9">
+        <v>46026</v>
+      </c>
+      <c r="B3" s="10">
+        <v>250</v>
+      </c>
+      <c r="C3" s="10">
+        <v>81</v>
+      </c>
+      <c r="D3" s="10">
+        <v>8</v>
+      </c>
+      <c r="E3" s="10">
+        <v>17</v>
+      </c>
+      <c r="F3" s="10">
+        <v>41</v>
+      </c>
+      <c r="G3" s="11"/>
+      <c r="H3" s="11"/>
+      <c r="I3" s="11"/>
+      <c r="J3" s="10">
+        <v>46</v>
+      </c>
+      <c r="K3" s="10">
+        <v>14</v>
+      </c>
+      <c r="L3" s="10">
         <v>11</v>
       </c>
-      <c r="K2" s="3" t="s">
+      <c r="M3" s="10">
+        <v>41</v>
+      </c>
+      <c r="N3" s="10">
+        <v>46</v>
+      </c>
+      <c r="O3" s="11"/>
+      <c r="P3" s="10">
         <v>5</v>
       </c>
-      <c r="L2" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="M2" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="N2" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="O2" s="3" t="s">
+      <c r="Q3" s="10">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="A4" s="9">
+        <v>46027</v>
+      </c>
+      <c r="B4" s="10">
+        <v>250</v>
+      </c>
+      <c r="C4" s="10">
+        <v>81</v>
+      </c>
+      <c r="D4" s="10">
+        <v>8</v>
+      </c>
+      <c r="E4" s="10">
+        <v>17</v>
+      </c>
+      <c r="F4" s="10">
+        <v>41</v>
+      </c>
+      <c r="G4" s="11"/>
+      <c r="H4" s="11"/>
+      <c r="I4" s="11"/>
+      <c r="J4" s="10">
+        <v>46</v>
+      </c>
+      <c r="K4" s="10">
+        <v>14</v>
+      </c>
+      <c r="L4" s="10">
+        <v>11</v>
+      </c>
+      <c r="M4" s="10">
+        <v>41</v>
+      </c>
+      <c r="N4" s="10">
+        <v>46</v>
+      </c>
+      <c r="O4" s="10">
+        <v>16</v>
+      </c>
+      <c r="P4" s="10">
+        <v>5</v>
+      </c>
+      <c r="Q4" s="11"/>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="A5" s="9">
+        <v>46028</v>
+      </c>
+      <c r="B5" s="10">
+        <v>250</v>
+      </c>
+      <c r="C5" s="10">
+        <v>81</v>
+      </c>
+      <c r="D5" s="10">
+        <v>8</v>
+      </c>
+      <c r="E5" s="10">
+        <v>17</v>
+      </c>
+      <c r="F5" s="10">
+        <v>41</v>
+      </c>
+      <c r="G5" s="11"/>
+      <c r="H5" s="11"/>
+      <c r="I5" s="10">
+        <v>10</v>
+      </c>
+      <c r="J5" s="10">
+        <v>46</v>
+      </c>
+      <c r="K5" s="10">
+        <v>14</v>
+      </c>
+      <c r="L5" s="10">
+        <v>11</v>
+      </c>
+      <c r="M5" s="10">
+        <v>41</v>
+      </c>
+      <c r="N5" s="10">
+        <v>46</v>
+      </c>
+      <c r="O5" s="10">
+        <v>16</v>
+      </c>
+      <c r="P5" s="10">
+        <v>5</v>
+      </c>
+      <c r="Q5" s="11"/>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="A6" s="9">
+        <v>46029</v>
+      </c>
+      <c r="B6" s="10">
+        <v>250</v>
+      </c>
+      <c r="C6" s="10">
+        <v>81</v>
+      </c>
+      <c r="D6" s="10">
+        <v>8</v>
+      </c>
+      <c r="E6" s="10">
+        <v>17</v>
+      </c>
+      <c r="F6" s="10">
+        <v>41</v>
+      </c>
+      <c r="G6" s="11"/>
+      <c r="H6" s="11"/>
+      <c r="I6" s="11"/>
+      <c r="J6" s="10">
+        <v>46</v>
+      </c>
+      <c r="K6" s="10">
+        <v>14</v>
+      </c>
+      <c r="L6" s="10">
+        <v>11</v>
+      </c>
+      <c r="M6" s="10">
+        <v>41</v>
+      </c>
+      <c r="N6" s="10">
+        <v>46</v>
+      </c>
+      <c r="O6" s="10">
+        <v>16</v>
+      </c>
+      <c r="P6" s="10">
+        <v>5</v>
+      </c>
+      <c r="Q6" s="10">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="A7" s="9">
+        <v>46030</v>
+      </c>
+      <c r="B7" s="10">
+        <v>210</v>
+      </c>
+      <c r="C7" s="10">
+        <v>102</v>
+      </c>
+      <c r="D7" s="10">
+        <v>10</v>
+      </c>
+      <c r="E7" s="10">
         <v>23</v>
       </c>
-      <c r="P2" s="3" t="s">
+      <c r="F7" s="10">
+        <v>47</v>
+      </c>
+      <c r="G7" s="11"/>
+      <c r="H7" s="11"/>
+      <c r="I7" s="11"/>
+      <c r="J7" s="10">
+        <v>63</v>
+      </c>
+      <c r="K7" s="10">
+        <v>30</v>
+      </c>
+      <c r="L7" s="10">
+        <v>10</v>
+      </c>
+      <c r="M7" s="10">
+        <v>46</v>
+      </c>
+      <c r="N7" s="10">
+        <v>50</v>
+      </c>
+      <c r="O7" s="11"/>
+      <c r="P7" s="10">
+        <v>3</v>
+      </c>
+      <c r="Q7" s="11"/>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="A8" s="9">
+        <v>46031</v>
+      </c>
+      <c r="B8" s="10">
+        <v>210</v>
+      </c>
+      <c r="C8" s="10">
+        <v>102</v>
+      </c>
+      <c r="D8" s="10">
+        <v>10</v>
+      </c>
+      <c r="E8" s="10">
+        <v>23</v>
+      </c>
+      <c r="F8" s="10">
+        <v>47</v>
+      </c>
+      <c r="G8" s="11"/>
+      <c r="H8" s="11"/>
+      <c r="I8" s="11"/>
+      <c r="J8" s="10">
+        <v>63</v>
+      </c>
+      <c r="K8" s="10">
+        <v>30</v>
+      </c>
+      <c r="L8" s="10">
+        <v>10</v>
+      </c>
+      <c r="M8" s="10">
+        <v>46</v>
+      </c>
+      <c r="N8" s="10">
+        <v>50</v>
+      </c>
+      <c r="O8" s="10">
+        <v>16</v>
+      </c>
+      <c r="P8" s="10">
+        <v>3</v>
+      </c>
+      <c r="Q8" s="11"/>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="A9" s="9">
+        <v>46032</v>
+      </c>
+      <c r="B9" s="10">
+        <v>210</v>
+      </c>
+      <c r="C9" s="10">
+        <v>102</v>
+      </c>
+      <c r="D9" s="10">
+        <v>10</v>
+      </c>
+      <c r="E9" s="10">
+        <v>23</v>
+      </c>
+      <c r="F9" s="10">
+        <v>47</v>
+      </c>
+      <c r="G9" s="11"/>
+      <c r="H9" s="11"/>
+      <c r="I9" s="10">
+        <v>11</v>
+      </c>
+      <c r="J9" s="10">
+        <v>63</v>
+      </c>
+      <c r="K9" s="10">
+        <v>30</v>
+      </c>
+      <c r="L9" s="10">
+        <v>10</v>
+      </c>
+      <c r="M9" s="10">
+        <v>46</v>
+      </c>
+      <c r="N9" s="10">
+        <v>50</v>
+      </c>
+      <c r="O9" s="10">
+        <v>16</v>
+      </c>
+      <c r="P9" s="10">
+        <v>3</v>
+      </c>
+      <c r="Q9" s="11"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="A10" s="9">
+        <v>46033</v>
+      </c>
+      <c r="B10" s="10">
+        <v>210</v>
+      </c>
+      <c r="C10" s="10">
+        <v>102</v>
+      </c>
+      <c r="D10" s="10">
+        <v>10</v>
+      </c>
+      <c r="E10" s="10">
+        <v>23</v>
+      </c>
+      <c r="F10" s="10">
+        <v>47</v>
+      </c>
+      <c r="G10" s="11"/>
+      <c r="H10" s="11"/>
+      <c r="I10" s="11"/>
+      <c r="J10" s="10">
+        <v>63</v>
+      </c>
+      <c r="K10" s="10">
+        <v>30</v>
+      </c>
+      <c r="L10" s="10">
+        <v>10</v>
+      </c>
+      <c r="M10" s="10">
+        <v>46</v>
+      </c>
+      <c r="N10" s="10">
+        <v>50</v>
+      </c>
+      <c r="O10" s="10">
+        <v>16</v>
+      </c>
+      <c r="P10" s="11"/>
+      <c r="Q10" s="11"/>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="A11" s="9">
+        <v>46034</v>
+      </c>
+      <c r="B11" s="10">
+        <v>230</v>
+      </c>
+      <c r="C11" s="10">
+        <v>113</v>
+      </c>
+      <c r="D11" s="11"/>
+      <c r="E11" s="10">
+        <v>23</v>
+      </c>
+      <c r="F11" s="10">
+        <v>49</v>
+      </c>
+      <c r="G11" s="10">
+        <v>11</v>
+      </c>
+      <c r="H11" s="11"/>
+      <c r="I11" s="11"/>
+      <c r="J11" s="10">
+        <v>61</v>
+      </c>
+      <c r="K11" s="11"/>
+      <c r="L11" s="11"/>
+      <c r="M11" s="11"/>
+      <c r="N11" s="11"/>
+      <c r="O11" s="11"/>
+      <c r="P11" s="11"/>
+      <c r="Q11" s="11"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="A12" s="9">
+        <v>46035</v>
+      </c>
+      <c r="B12" s="10">
+        <v>229</v>
+      </c>
+      <c r="C12" s="10">
+        <v>105</v>
+      </c>
+      <c r="D12" s="11"/>
+      <c r="E12" s="10">
+        <v>23</v>
+      </c>
+      <c r="F12" s="10">
+        <v>47</v>
+      </c>
+      <c r="G12" s="10">
         <v>8</v>
       </c>
-      <c r="Q2" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="R2" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="S2" s="1"/>
-    </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.45">
-      <c r="A3" s="13">
-        <v>46026</v>
-      </c>
-      <c r="B3" s="14">
-        <v>250</v>
-      </c>
-      <c r="C3" s="14">
-        <v>81</v>
-      </c>
-      <c r="D3" s="14">
+      <c r="H12" s="11"/>
+      <c r="I12" s="11"/>
+      <c r="J12" s="10">
+        <v>65</v>
+      </c>
+      <c r="K12" s="11"/>
+      <c r="L12" s="11"/>
+      <c r="M12" s="11"/>
+      <c r="N12" s="11"/>
+      <c r="O12" s="11"/>
+      <c r="P12" s="11"/>
+      <c r="Q12" s="11"/>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="A13" s="9">
+        <v>46096</v>
+      </c>
+      <c r="B13" s="10">
+        <v>218</v>
+      </c>
+      <c r="C13" s="10">
+        <v>119</v>
+      </c>
+      <c r="D13" s="11"/>
+      <c r="E13" s="10">
+        <v>23</v>
+      </c>
+      <c r="F13" s="10">
+        <v>37</v>
+      </c>
+      <c r="G13" s="10">
+        <v>10</v>
+      </c>
+      <c r="H13" s="10">
+        <v>185</v>
+      </c>
+      <c r="I13" s="11"/>
+      <c r="J13" s="10">
+        <v>69</v>
+      </c>
+      <c r="K13" s="11"/>
+      <c r="L13" s="11"/>
+      <c r="M13" s="11"/>
+      <c r="N13" s="11"/>
+      <c r="O13" s="11"/>
+      <c r="P13" s="11"/>
+      <c r="Q13" s="11"/>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="A14" s="9">
+        <v>46103</v>
+      </c>
+      <c r="B14" s="10">
+        <v>233</v>
+      </c>
+      <c r="C14" s="10">
+        <v>108</v>
+      </c>
+      <c r="D14" s="11"/>
+      <c r="E14" s="10">
+        <v>18</v>
+      </c>
+      <c r="F14" s="10">
+        <v>44</v>
+      </c>
+      <c r="G14" s="10">
         <v>8</v>
       </c>
-      <c r="E3" s="14">
-        <v>17</v>
-      </c>
-      <c r="F3" s="14">
-        <v>41</v>
-      </c>
-      <c r="G3" s="15"/>
-      <c r="H3" s="15"/>
-      <c r="I3" s="15"/>
-      <c r="J3" s="14">
-        <v>46</v>
-      </c>
-      <c r="K3" s="14">
-        <v>14</v>
-      </c>
-      <c r="L3" s="14">
-        <v>11</v>
-      </c>
-      <c r="M3" s="14">
-        <v>41</v>
-      </c>
-      <c r="N3" s="14">
-        <v>46</v>
-      </c>
-      <c r="O3" s="15"/>
-      <c r="P3" s="14">
-        <v>5</v>
-      </c>
-      <c r="Q3" s="14">
-        <v>18</v>
-      </c>
-      <c r="R3" s="5"/>
-    </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.45">
-      <c r="A4" s="13">
-        <v>46033</v>
-      </c>
-      <c r="B4" s="14">
-        <v>250</v>
-      </c>
-      <c r="C4" s="14">
-        <v>81</v>
-      </c>
-      <c r="D4" s="14">
+      <c r="H14" s="10">
+        <v>324</v>
+      </c>
+      <c r="I14" s="11"/>
+      <c r="J14" s="10">
+        <v>55</v>
+      </c>
+      <c r="K14" s="11"/>
+      <c r="L14" s="11"/>
+      <c r="M14" s="11"/>
+      <c r="N14" s="11"/>
+      <c r="O14" s="11"/>
+      <c r="P14" s="11"/>
+      <c r="Q14" s="11"/>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="A15" s="9">
+        <v>46110</v>
+      </c>
+      <c r="B15" s="10">
+        <v>213</v>
+      </c>
+      <c r="C15" s="10">
+        <v>105</v>
+      </c>
+      <c r="D15" s="11"/>
+      <c r="E15" s="10">
+        <v>21</v>
+      </c>
+      <c r="F15" s="10">
+        <v>78</v>
+      </c>
+      <c r="G15" s="10">
         <v>8</v>
       </c>
-      <c r="E4" s="14">
-        <v>17</v>
-      </c>
-      <c r="F4" s="14">
-        <v>41</v>
-      </c>
-      <c r="G4" s="15"/>
-      <c r="H4" s="15"/>
-      <c r="I4" s="15"/>
-      <c r="J4" s="14">
-        <v>46</v>
-      </c>
-      <c r="K4" s="14">
-        <v>14</v>
-      </c>
-      <c r="L4" s="14">
-        <v>11</v>
-      </c>
-      <c r="M4" s="14">
-        <v>41</v>
-      </c>
-      <c r="N4" s="14">
-        <v>46</v>
-      </c>
-      <c r="O4" s="14">
-        <v>16</v>
-      </c>
-      <c r="P4" s="14">
-        <v>5</v>
-      </c>
-      <c r="Q4" s="15"/>
-      <c r="R4" s="5"/>
-    </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.45">
-      <c r="A5" s="13">
-        <v>46040</v>
-      </c>
-      <c r="B5" s="14">
-        <v>250</v>
-      </c>
-      <c r="C5" s="14">
-        <v>81</v>
-      </c>
-      <c r="D5" s="14">
-        <v>8</v>
-      </c>
-      <c r="E5" s="14">
-        <v>17</v>
-      </c>
-      <c r="F5" s="14">
-        <v>41</v>
-      </c>
-      <c r="G5" s="15"/>
-      <c r="H5" s="15"/>
-      <c r="I5" s="14">
-        <v>10</v>
-      </c>
-      <c r="J5" s="14">
-        <v>46</v>
-      </c>
-      <c r="K5" s="14">
-        <v>14</v>
-      </c>
-      <c r="L5" s="14">
-        <v>11</v>
-      </c>
-      <c r="M5" s="14">
-        <v>41</v>
-      </c>
-      <c r="N5" s="14">
-        <v>46</v>
-      </c>
-      <c r="O5" s="14">
-        <v>16</v>
-      </c>
-      <c r="P5" s="14">
-        <v>5</v>
-      </c>
-      <c r="Q5" s="15"/>
-      <c r="R5" s="5"/>
-    </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.45">
-      <c r="A6" s="13">
-        <v>46047</v>
-      </c>
-      <c r="B6" s="14">
-        <v>250</v>
-      </c>
-      <c r="C6" s="14">
-        <v>81</v>
-      </c>
-      <c r="D6" s="14">
-        <v>8</v>
-      </c>
-      <c r="E6" s="14">
-        <v>17</v>
-      </c>
-      <c r="F6" s="14">
-        <v>41</v>
-      </c>
-      <c r="G6" s="15"/>
-      <c r="H6" s="15"/>
-      <c r="I6" s="15"/>
-      <c r="J6" s="14">
-        <v>46</v>
-      </c>
-      <c r="K6" s="14">
-        <v>14</v>
-      </c>
-      <c r="L6" s="14">
-        <v>11</v>
-      </c>
-      <c r="M6" s="14">
-        <v>41</v>
-      </c>
-      <c r="N6" s="14">
-        <v>46</v>
-      </c>
-      <c r="O6" s="14">
-        <v>16</v>
-      </c>
-      <c r="P6" s="14">
-        <v>5</v>
-      </c>
-      <c r="Q6" s="14">
-        <v>14</v>
-      </c>
-      <c r="R6" s="5">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.45">
-      <c r="A7" s="13">
-        <v>46054</v>
-      </c>
-      <c r="B7" s="14">
-        <v>210</v>
-      </c>
-      <c r="C7" s="14">
-        <v>102</v>
-      </c>
-      <c r="D7" s="14">
-        <v>10</v>
-      </c>
-      <c r="E7" s="14">
-        <v>23</v>
-      </c>
-      <c r="F7" s="14">
-        <v>47</v>
-      </c>
-      <c r="G7" s="15"/>
-      <c r="H7" s="15"/>
-      <c r="I7" s="15"/>
-      <c r="J7" s="14">
-        <v>63</v>
-      </c>
-      <c r="K7" s="14">
-        <v>30</v>
-      </c>
-      <c r="L7" s="14">
-        <v>10</v>
-      </c>
-      <c r="M7" s="14">
-        <v>46</v>
-      </c>
-      <c r="N7" s="14">
-        <v>50</v>
-      </c>
-      <c r="O7" s="15"/>
-      <c r="P7" s="14">
-        <v>3</v>
-      </c>
-      <c r="Q7" s="15"/>
-      <c r="R7" s="5"/>
-    </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.45">
-      <c r="A8" s="13">
-        <v>46061</v>
-      </c>
-      <c r="B8" s="14">
-        <v>210</v>
-      </c>
-      <c r="C8" s="14">
-        <v>102</v>
-      </c>
-      <c r="D8" s="14">
-        <v>10</v>
-      </c>
-      <c r="E8" s="14">
-        <v>23</v>
-      </c>
-      <c r="F8" s="14">
-        <v>47</v>
-      </c>
-      <c r="G8" s="15"/>
-      <c r="H8" s="15"/>
-      <c r="I8" s="15"/>
-      <c r="J8" s="14">
-        <v>63</v>
-      </c>
-      <c r="K8" s="14">
-        <v>30</v>
-      </c>
-      <c r="L8" s="14">
-        <v>10</v>
-      </c>
-      <c r="M8" s="14">
-        <v>46</v>
-      </c>
-      <c r="N8" s="14">
-        <v>50</v>
-      </c>
-      <c r="O8" s="14">
-        <v>16</v>
-      </c>
-      <c r="P8" s="14">
-        <v>3</v>
-      </c>
-      <c r="Q8" s="15"/>
-      <c r="R8" s="5"/>
-    </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.45">
-      <c r="A9" s="13">
-        <v>46068</v>
-      </c>
-      <c r="B9" s="14">
-        <v>210</v>
-      </c>
-      <c r="C9" s="14">
-        <v>102</v>
-      </c>
-      <c r="D9" s="14">
-        <v>10</v>
-      </c>
-      <c r="E9" s="14">
-        <v>23</v>
-      </c>
-      <c r="F9" s="14">
-        <v>47</v>
-      </c>
-      <c r="G9" s="15"/>
-      <c r="H9" s="15"/>
-      <c r="I9" s="14">
-        <v>11</v>
-      </c>
-      <c r="J9" s="14">
-        <v>63</v>
-      </c>
-      <c r="K9" s="14">
-        <v>30</v>
-      </c>
-      <c r="L9" s="14">
-        <v>10</v>
-      </c>
-      <c r="M9" s="14">
-        <v>46</v>
-      </c>
-      <c r="N9" s="14">
-        <v>50</v>
-      </c>
-      <c r="O9" s="14">
-        <v>16</v>
-      </c>
-      <c r="P9" s="14">
-        <v>3</v>
-      </c>
-      <c r="Q9" s="15"/>
-      <c r="R9" s="5"/>
-    </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.45">
-      <c r="A10" s="13">
-        <v>46075</v>
-      </c>
-      <c r="B10" s="14">
-        <v>210</v>
-      </c>
-      <c r="C10" s="14">
-        <v>102</v>
-      </c>
-      <c r="D10" s="14">
-        <v>10</v>
-      </c>
-      <c r="E10" s="14">
-        <v>23</v>
-      </c>
-      <c r="F10" s="14">
-        <v>47</v>
-      </c>
-      <c r="G10" s="15"/>
-      <c r="H10" s="15"/>
-      <c r="I10" s="15"/>
-      <c r="J10" s="14">
-        <v>63</v>
-      </c>
-      <c r="K10" s="14">
-        <v>30</v>
-      </c>
-      <c r="L10" s="14">
-        <v>10</v>
-      </c>
-      <c r="M10" s="14">
-        <v>46</v>
-      </c>
-      <c r="N10" s="14">
-        <v>50</v>
-      </c>
-      <c r="O10" s="14">
-        <v>16</v>
-      </c>
-      <c r="P10" s="15"/>
-      <c r="Q10" s="15"/>
-      <c r="R10" s="5"/>
-    </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.45">
-      <c r="A11" s="13">
-        <v>46082</v>
-      </c>
-      <c r="B11" s="14">
-        <v>230</v>
-      </c>
-      <c r="C11" s="14">
-        <v>113</v>
-      </c>
-      <c r="D11" s="15"/>
-      <c r="E11" s="14">
-        <v>23</v>
-      </c>
-      <c r="F11" s="14">
-        <v>49</v>
-      </c>
-      <c r="G11" s="14">
-        <v>11</v>
-      </c>
-      <c r="H11" s="15"/>
-      <c r="I11" s="15"/>
-      <c r="J11" s="14">
-        <v>61</v>
-      </c>
-      <c r="K11" s="15"/>
-      <c r="L11" s="15"/>
-      <c r="M11" s="15"/>
-      <c r="N11" s="15"/>
-      <c r="O11" s="15"/>
-      <c r="P11" s="15"/>
-      <c r="Q11" s="15"/>
-      <c r="R11" s="5"/>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.45">
-      <c r="A12" s="13">
-        <v>46089</v>
-      </c>
-      <c r="B12" s="14">
-        <v>229</v>
-      </c>
-      <c r="C12" s="14">
-        <v>105</v>
-      </c>
-      <c r="D12" s="15"/>
-      <c r="E12" s="14">
-        <v>23</v>
-      </c>
-      <c r="F12" s="14">
-        <v>47</v>
-      </c>
-      <c r="G12" s="14">
-        <v>8</v>
-      </c>
-      <c r="H12" s="15"/>
-      <c r="I12" s="15"/>
-      <c r="J12" s="14">
-        <v>65</v>
-      </c>
-      <c r="K12" s="15"/>
-      <c r="L12" s="15"/>
-      <c r="M12" s="15"/>
-      <c r="N12" s="15"/>
-      <c r="O12" s="15"/>
-      <c r="P12" s="15"/>
-      <c r="Q12" s="15"/>
-      <c r="R12" s="5"/>
-    </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.45">
-      <c r="A13" s="13">
-        <v>46096</v>
-      </c>
-      <c r="B13" s="14">
-        <v>218</v>
-      </c>
-      <c r="C13" s="14">
-        <v>119</v>
-      </c>
-      <c r="D13" s="15"/>
-      <c r="E13" s="14">
-        <v>23</v>
-      </c>
-      <c r="F13" s="14">
-        <v>37</v>
-      </c>
-      <c r="G13" s="14">
-        <v>10</v>
-      </c>
-      <c r="H13" s="14">
-        <v>185</v>
-      </c>
-      <c r="I13" s="15"/>
-      <c r="J13" s="14">
-        <v>69</v>
-      </c>
-      <c r="K13" s="15"/>
-      <c r="L13" s="15"/>
-      <c r="M13" s="15"/>
-      <c r="N13" s="15"/>
-      <c r="O13" s="15"/>
-      <c r="P13" s="15"/>
-      <c r="Q13" s="15"/>
-      <c r="R13" s="5"/>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.45">
-      <c r="A14" s="13">
-        <v>46103</v>
-      </c>
-      <c r="B14" s="14">
-        <v>233</v>
-      </c>
-      <c r="C14" s="14">
-        <v>108</v>
-      </c>
-      <c r="D14" s="15"/>
-      <c r="E14" s="14">
-        <v>18</v>
-      </c>
-      <c r="F14" s="14">
-        <v>44</v>
-      </c>
-      <c r="G14" s="14">
-        <v>8</v>
-      </c>
-      <c r="H14" s="14">
-        <v>324</v>
-      </c>
-      <c r="I14" s="15"/>
-      <c r="J14" s="14">
-        <v>55</v>
-      </c>
-      <c r="K14" s="15"/>
-      <c r="L14" s="15"/>
-      <c r="M14" s="15"/>
-      <c r="N14" s="15"/>
-      <c r="O14" s="15"/>
-      <c r="P14" s="15"/>
-      <c r="Q14" s="15"/>
-      <c r="R14" s="5"/>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.45">
-      <c r="A15" s="13">
-        <v>46110</v>
-      </c>
-      <c r="B15" s="14">
-        <v>213</v>
-      </c>
-      <c r="C15" s="14">
-        <v>105</v>
-      </c>
-      <c r="D15" s="15"/>
-      <c r="E15" s="14">
-        <v>21</v>
-      </c>
-      <c r="F15" s="14">
-        <v>78</v>
-      </c>
-      <c r="G15" s="14">
-        <v>8</v>
-      </c>
-      <c r="H15" s="15"/>
-      <c r="I15" s="15"/>
-      <c r="J15" s="14">
+      <c r="H15" s="11"/>
+      <c r="I15" s="11"/>
+      <c r="J15" s="10">
         <v>60</v>
       </c>
-      <c r="K15" s="15"/>
-      <c r="L15" s="15"/>
-      <c r="M15" s="15"/>
-      <c r="N15" s="15"/>
-      <c r="O15" s="15"/>
-      <c r="P15" s="15"/>
-      <c r="Q15" s="15"/>
-      <c r="R15" s="5"/>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.45">
-      <c r="A16" s="13">
+      <c r="K15" s="11"/>
+      <c r="L15" s="11"/>
+      <c r="M15" s="11"/>
+      <c r="N15" s="11"/>
+      <c r="O15" s="11"/>
+      <c r="P15" s="11"/>
+      <c r="Q15" s="11"/>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="A16" s="9">
         <v>46117</v>
       </c>
-      <c r="B16" s="15"/>
-      <c r="C16" s="15"/>
-      <c r="D16" s="15"/>
-      <c r="E16" s="15"/>
-      <c r="F16" s="15"/>
-      <c r="G16" s="15"/>
-      <c r="H16" s="15"/>
-      <c r="I16" s="15"/>
-      <c r="J16" s="15"/>
-      <c r="K16" s="15"/>
-      <c r="L16" s="15"/>
-      <c r="M16" s="15"/>
-      <c r="N16" s="15"/>
-      <c r="O16" s="15"/>
-      <c r="P16" s="15"/>
-      <c r="Q16" s="15"/>
-      <c r="R16" s="5"/>
-    </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="B16" s="11"/>
+      <c r="C16" s="11"/>
+      <c r="D16" s="11"/>
+      <c r="E16" s="11"/>
+      <c r="F16" s="11"/>
+      <c r="G16" s="11"/>
+      <c r="H16" s="11"/>
+      <c r="I16" s="11"/>
+      <c r="J16" s="11"/>
+      <c r="K16" s="11"/>
+      <c r="L16" s="11"/>
+      <c r="M16" s="11"/>
+      <c r="N16" s="11"/>
+      <c r="O16" s="11"/>
+      <c r="P16" s="11"/>
+      <c r="Q16" s="5"/>
+    </row>
+    <row r="17" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A17" s="7">
         <v>46124</v>
       </c>
@@ -1279,10 +1252,9 @@
       <c r="N17" s="8"/>
       <c r="O17" s="8"/>
       <c r="P17" s="8"/>
-      <c r="Q17" s="8"/>
-      <c r="R17" s="5"/>
-    </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="Q17" s="5"/>
+    </row>
+    <row r="18" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A18" s="7">
         <v>46131</v>
       </c>
@@ -1301,10 +1273,9 @@
       <c r="N18" s="8"/>
       <c r="O18" s="8"/>
       <c r="P18" s="8"/>
-      <c r="Q18" s="8"/>
-      <c r="R18" s="5"/>
-    </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="Q18" s="5"/>
+    </row>
+    <row r="19" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A19" s="7">
         <v>46079</v>
       </c>
@@ -1323,10 +1294,9 @@
       <c r="N19" s="8"/>
       <c r="O19" s="8"/>
       <c r="P19" s="8"/>
-      <c r="Q19" s="8"/>
-      <c r="R19" s="5"/>
-    </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="Q19" s="5"/>
+    </row>
+    <row r="20" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A20" s="4"/>
       <c r="B20" s="4"/>
       <c r="C20" s="4"/>
@@ -1344,9 +1314,8 @@
       <c r="O20" s="4"/>
       <c r="P20" s="4"/>
       <c r="Q20" s="4"/>
-      <c r="R20" s="4"/>
-    </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.45">
+    </row>
+    <row r="21" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A21" s="4"/>
       <c r="B21" s="4"/>
       <c r="C21" s="4"/>
@@ -1364,9 +1333,8 @@
       <c r="O21" s="4"/>
       <c r="P21" s="4"/>
       <c r="Q21" s="4"/>
-      <c r="R21" s="4"/>
-    </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.45">
+    </row>
+    <row r="22" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A22" s="4"/>
       <c r="B22" s="4"/>
       <c r="C22" s="4"/>
@@ -1384,9 +1352,8 @@
       <c r="O22" s="4"/>
       <c r="P22" s="4"/>
       <c r="Q22" s="4"/>
-      <c r="R22" s="4"/>
-    </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.45">
+    </row>
+    <row r="23" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A23" s="4"/>
       <c r="B23" s="4"/>
       <c r="C23" s="4"/>
@@ -1404,9 +1371,8 @@
       <c r="O23" s="4"/>
       <c r="P23" s="4"/>
       <c r="Q23" s="4"/>
-      <c r="R23" s="4"/>
-    </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.45">
+    </row>
+    <row r="24" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A24" s="4"/>
       <c r="B24" s="4"/>
       <c r="C24" s="4"/>
@@ -1424,9 +1390,8 @@
       <c r="O24" s="4"/>
       <c r="P24" s="4"/>
       <c r="Q24" s="4"/>
-      <c r="R24" s="4"/>
-    </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.45">
+    </row>
+    <row r="25" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A25" s="4"/>
       <c r="B25" s="4"/>
       <c r="C25" s="4"/>
@@ -1444,9 +1409,8 @@
       <c r="O25" s="4"/>
       <c r="P25" s="4"/>
       <c r="Q25" s="4"/>
-      <c r="R25" s="4"/>
-    </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.45">
+    </row>
+    <row r="26" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A26" s="4"/>
       <c r="B26" s="4"/>
       <c r="C26" s="4"/>
@@ -1464,9 +1428,8 @@
       <c r="O26" s="4"/>
       <c r="P26" s="4"/>
       <c r="Q26" s="4"/>
-      <c r="R26" s="4"/>
-    </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.45">
+    </row>
+    <row r="27" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A27" s="4"/>
       <c r="B27" s="4"/>
       <c r="C27" s="4"/>
@@ -1484,9 +1447,8 @@
       <c r="O27" s="4"/>
       <c r="P27" s="4"/>
       <c r="Q27" s="4"/>
-      <c r="R27" s="4"/>
-    </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.45">
+    </row>
+    <row r="28" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A28" s="4"/>
       <c r="B28" s="4"/>
       <c r="C28" s="4"/>
@@ -1504,9 +1466,8 @@
       <c r="O28" s="4"/>
       <c r="P28" s="4"/>
       <c r="Q28" s="4"/>
-      <c r="R28" s="4"/>
-    </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.45">
+    </row>
+    <row r="29" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A29" s="4"/>
       <c r="B29" s="4"/>
       <c r="C29" s="4"/>
@@ -1524,9 +1485,8 @@
       <c r="O29" s="4"/>
       <c r="P29" s="4"/>
       <c r="Q29" s="4"/>
-      <c r="R29" s="4"/>
-    </row>
-    <row r="30" spans="1:18" x14ac:dyDescent="0.45">
+    </row>
+    <row r="30" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A30" s="4"/>
       <c r="B30" s="4"/>
       <c r="C30" s="4"/>
@@ -1544,9 +1504,8 @@
       <c r="O30" s="4"/>
       <c r="P30" s="4"/>
       <c r="Q30" s="4"/>
-      <c r="R30" s="4"/>
-    </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.45">
+    </row>
+    <row r="31" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A31" s="4"/>
       <c r="B31" s="4"/>
       <c r="C31" s="4"/>
@@ -1564,9 +1523,8 @@
       <c r="O31" s="4"/>
       <c r="P31" s="4"/>
       <c r="Q31" s="4"/>
-      <c r="R31" s="4"/>
-    </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.45">
+    </row>
+    <row r="32" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A32" s="4"/>
       <c r="B32" s="4"/>
       <c r="C32" s="4"/>
@@ -1584,9 +1542,8 @@
       <c r="O32" s="4"/>
       <c r="P32" s="4"/>
       <c r="Q32" s="4"/>
-      <c r="R32" s="4"/>
-    </row>
-    <row r="33" spans="1:18" x14ac:dyDescent="0.45">
+    </row>
+    <row r="33" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A33" s="4"/>
       <c r="B33" s="4"/>
       <c r="C33" s="4"/>
@@ -1604,15 +1561,14 @@
       <c r="O33" s="4"/>
       <c r="P33" s="4"/>
       <c r="Q33" s="4"/>
-      <c r="R33" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:H1"/>
-    <mergeCell ref="K1:L1"/>
-    <mergeCell ref="I1:J1"/>
-    <mergeCell ref="M1:O1"/>
+    <mergeCell ref="B1:G1"/>
+    <mergeCell ref="J1:K1"/>
+    <mergeCell ref="H1:I1"/>
+    <mergeCell ref="L1:N1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
